--- a/kb/openclassrooms_out/20260929_OpenClassrooms_Digital_Marketer_CPL_Crosswalk_2.xlsx
+++ b/kb/openclassrooms_out/20260929_OpenClassrooms_Digital_Marketer_CPL_Crosswalk_2.xlsx
@@ -536,7 +536,7 @@
     <row r="2" ht="25.5" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>0614.00: Digital Media (TOP; verify)</t>
+          <t>Digital Media</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -598,7 +598,7 @@
     <row r="3" ht="25.5" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -660,7 +660,7 @@
     <row r="4" ht="25.5" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0614.30: Website Design and Development (TOP; verify)</t>
+          <t>Website Design and Development</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -722,7 +722,7 @@
     <row r="5" ht="25.5" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
     <row r="6" ht="25.5" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -846,7 +846,7 @@
     <row r="7" ht="25.5" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0614.30: Website Design and Development (TOP; verify)</t>
+          <t>Website Design and Development</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
     <row r="8" ht="25.5" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -970,7 +970,7 @@
     <row r="9" ht="25.5" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1032,7 +1032,7 @@
     <row r="10" ht="25.5" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1094,7 +1094,7 @@
     <row r="11" ht="25.5" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1156,7 +1156,7 @@
     <row r="12" ht="25.5" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1218,7 +1218,7 @@
     <row r="13" ht="25.5" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1276,7 +1276,7 @@
     <row r="14" ht="25.5" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1334,7 +1334,7 @@
     <row r="15" ht="25.5" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="16" ht="25.5" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
     <row r="17" ht="25.5" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1520,7 +1520,7 @@
     <row r="18" ht="25.5" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
     <row r="19" ht="25.5" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1644,7 +1644,7 @@
     <row r="20" ht="25.5" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1706,7 +1706,7 @@
     <row r="21" ht="25.5" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1768,7 +1768,7 @@
     <row r="22" ht="25.5" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1830,7 +1830,7 @@
     <row r="23" ht="25.5" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1892,7 +1892,7 @@
     <row r="24" ht="25.5" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1954,7 +1954,7 @@
     <row r="25" ht="25.5" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -2016,7 +2016,7 @@
     <row r="26" ht="25.5" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -2074,7 +2074,7 @@
     <row r="27" ht="25.5" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
     <row r="28" ht="25.5" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -2198,7 +2198,7 @@
     <row r="29" ht="25.5" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -2260,7 +2260,7 @@
     <row r="30" ht="25.5" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -2322,7 +2322,7 @@
     <row r="31" ht="25.5" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
     <row r="32" ht="25.5" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
     <row r="33" ht="25.5" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -2508,7 +2508,7 @@
     <row r="34" ht="25.5" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>0614.30: Website Design and Development (TOP; verify)</t>
+          <t>Website Design and Development</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2570,7 +2570,7 @@
     <row r="35" ht="25.5" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>0614.30: Website Design and Development (TOP; verify)</t>
+          <t>Website Design and Development</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
     <row r="36" ht="25.5" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0614.30: Website Design and Development (TOP; verify)</t>
+          <t>Website Design and Development</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2694,7 +2694,7 @@
     <row r="37" ht="25.5" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0614.30: Website Design and Development (TOP; verify)</t>
+          <t>Website Design and Development</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
     <row r="38" ht="25.5" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2818,7 +2818,7 @@
     <row r="39" ht="25.5" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
     <row r="40" ht="25.5" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2938,7 +2938,7 @@
     <row r="41" ht="25.5" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1013.00: Commercial Art (TOP; verify)</t>
+          <t>Commercial Art</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -3000,7 +3000,7 @@
     <row r="42" ht="25.5" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -3062,7 +3062,7 @@
     <row r="43" ht="25.5" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -3124,7 +3124,7 @@
     <row r="44" ht="25.5" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
     <row r="45" ht="25.5" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -3248,7 +3248,7 @@
     <row r="46" ht="25.5" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -3310,7 +3310,7 @@
     <row r="47" ht="25.5" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -3372,7 +3372,7 @@
     <row r="48" ht="25.5" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -3434,7 +3434,7 @@
     <row r="49" ht="25.5" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>0506.00: Business Management (TOP; verify)</t>
+          <t>Business Management</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
     <row r="50" ht="25.5" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -3558,7 +3558,7 @@
     <row r="51" ht="25.5" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -3620,7 +3620,7 @@
     <row r="52" ht="25.5" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -3682,7 +3682,7 @@
     <row r="53" ht="25.5" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -3744,7 +3744,7 @@
     <row r="54" ht="25.5" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>0505.00: Business Administration (TOP; verify)</t>
+          <t>Business Administration</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -3806,7 +3806,7 @@
     <row r="55" ht="25.5" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -3868,7 +3868,7 @@
     <row r="56" ht="25.5" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>0509.70: E-Commerce (Business emphasis) (TOP; verify)</t>
+          <t>E-Commerce (Business emphasis)</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -3930,7 +3930,7 @@
     <row r="57" ht="25.5" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>0509.70: E-Commerce (Business emphasis) (TOP; verify)</t>
+          <t>E-Commerce (Business emphasis)</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -3992,7 +3992,7 @@
     <row r="58" ht="25.5" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>0509.10: Advertising (TOP; verify)</t>
+          <t>Advertising</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -4054,7 +4054,7 @@
     <row r="59" ht="25.5" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>0614.30: Website Design and Development (TOP; verify)</t>
+          <t>Website Design and Development</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -4116,7 +4116,7 @@
     <row r="60" ht="25.5" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>0506.40: Small Business and Entrepreneurship (TOP; verify)</t>
+          <t>Small Business and Entrepreneurship</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -4178,7 +4178,7 @@
     <row r="61" ht="25.5" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -4240,7 +4240,7 @@
     <row r="62" ht="25.5" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -4302,7 +4302,7 @@
     <row r="63" ht="25.5" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -4364,7 +4364,7 @@
     <row r="64" ht="25.5" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -4426,7 +4426,7 @@
     <row r="65" ht="25.5" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -4488,7 +4488,7 @@
     <row r="66" ht="25.5" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -4550,7 +4550,7 @@
     <row r="67" ht="25.5" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>0509.70: E-Commerce (Business emphasis) (TOP; verify)</t>
+          <t>E-Commerce (Business emphasis)</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -4612,7 +4612,7 @@
     <row r="68" ht="25.5" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>0509.70: E-Commerce (Business emphasis) (TOP; verify)</t>
+          <t>E-Commerce (Business emphasis)</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -4674,7 +4674,7 @@
     <row r="69" ht="25.5" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -4736,7 +4736,7 @@
     <row r="70" ht="25.5" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>0509.70: E-Commerce (Business emphasis) (TOP; verify)</t>
+          <t>E-Commerce (Business emphasis)</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -4798,7 +4798,7 @@
     <row r="71" ht="25.5" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -4860,7 +4860,7 @@
     <row r="72" ht="25.5" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -4922,7 +4922,7 @@
     <row r="73" ht="25.5" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -4984,7 +4984,7 @@
     <row r="74" ht="25.5" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -5004,7 +5004,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -5046,7 +5046,7 @@
     <row r="75" ht="25.5" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -5108,7 +5108,7 @@
     <row r="76" ht="25.5" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -5170,7 +5170,7 @@
     <row r="77" ht="25.5" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -5232,7 +5232,7 @@
     <row r="78" ht="25.5" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -5294,7 +5294,7 @@
     <row r="79" ht="25.5" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -5356,7 +5356,7 @@
     <row r="80" ht="25.5" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -5418,7 +5418,7 @@
     <row r="81" ht="25.5" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>0506.40: Small Business and Entrepreneurship (TOP; verify)</t>
+          <t>Small Business and Entrepreneurship</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -5480,7 +5480,7 @@
     <row r="82" ht="25.5" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -5500,7 +5500,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -5542,7 +5542,7 @@
     <row r="83" ht="25.5" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -5604,7 +5604,7 @@
     <row r="84" ht="25.5" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -5666,7 +5666,7 @@
     <row r="85" ht="25.5" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -5728,7 +5728,7 @@
     <row r="86" ht="25.5" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
     <row r="87" ht="25.5" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>0709.10: E-Commerce (Technology emphasis) (TOP; verify)</t>
+          <t>E-Commerce (Technology emphasis)</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -5852,7 +5852,7 @@
     <row r="88" ht="25.5" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -5914,7 +5914,7 @@
     <row r="89" ht="25.5" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -5976,7 +5976,7 @@
     <row r="90" ht="25.5" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -6038,7 +6038,7 @@
     <row r="91" ht="25.5" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>0514.00: Office Technology/Office Computer Applications (TOP; verify)</t>
+          <t>Office Technology/Office Computer Applications</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -6100,7 +6100,7 @@
     <row r="92" ht="25.5" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>0614.50: Desktop Publishing (TOP; verify)</t>
+          <t>Desktop Publishing</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -6162,7 +6162,7 @@
     <row r="93" ht="25.5" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>0699.00: Other Media and Communications (TOP; verify)</t>
+          <t>Other Media and Communications</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -6224,7 +6224,7 @@
     <row r="94" ht="25.5" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -6286,7 +6286,7 @@
     <row r="95" ht="25.5" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>0614.30: Website Design and Development (TOP; verify)</t>
+          <t>Website Design and Development</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -6348,7 +6348,7 @@
     <row r="96" ht="25.5" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>0614.30: Website Design and Development (TOP; verify)</t>
+          <t>Website Design and Development</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -6410,7 +6410,7 @@
     <row r="97" ht="25.5" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>0612.20: Film Production (TOP; verify)</t>
+          <t>Film Production</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -6472,7 +6472,7 @@
     <row r="98" ht="25.5" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -6534,7 +6534,7 @@
     <row r="99" ht="25.5" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -6596,7 +6596,7 @@
     <row r="100" ht="25.5" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -6658,7 +6658,7 @@
     <row r="101" ht="25.5" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
@@ -6720,7 +6720,7 @@
     <row r="102" ht="25.5" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -6782,7 +6782,7 @@
     <row r="103" ht="25.5" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
@@ -6844,7 +6844,7 @@
     <row r="104" ht="25.5" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -6864,7 +6864,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -6906,7 +6906,7 @@
     <row r="105" ht="25.5" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
@@ -6968,7 +6968,7 @@
     <row r="106" ht="25.5" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -7030,7 +7030,7 @@
     <row r="107" ht="25.5" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -7092,7 +7092,7 @@
     <row r="108" ht="25.5" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -7112,7 +7112,7 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>0506.40: Small Business and Entrepreneurship (TOP; verify)</t>
+          <t>Small Business and Entrepreneurship</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
@@ -7154,7 +7154,7 @@
     <row r="109" ht="25.5" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -7174,7 +7174,7 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>0610.00: Mass Communications (TOP; verify)</t>
+          <t>Mass Communications</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
@@ -7216,7 +7216,7 @@
     <row r="110" ht="25.5" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>0610.00: Mass Communications (TOP; verify)</t>
+          <t>Mass Communications</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -7278,7 +7278,7 @@
     <row r="111" ht="25.5" customHeight="1">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -7340,7 +7340,7 @@
     <row r="112" ht="25.5" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -7402,7 +7402,7 @@
     <row r="113" ht="25.5" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
@@ -7464,7 +7464,7 @@
     <row r="114" ht="25.5" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -7484,7 +7484,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
@@ -7526,7 +7526,7 @@
     <row r="115" ht="25.5" customHeight="1">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>0614.00: Digital Media (TOP; verify)</t>
+          <t>Digital Media</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
@@ -7588,7 +7588,7 @@
     <row r="116" ht="25.5" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>0509.10: Advertising (TOP; verify)</t>
+          <t>Advertising</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
@@ -7650,7 +7650,7 @@
     <row r="117" ht="25.5" customHeight="1">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -7712,7 +7712,7 @@
     <row r="118" ht="25.5" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -7732,7 +7732,7 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>0506.40: Small Business and Entrepreneurship (TOP; verify)</t>
+          <t>Small Business and Entrepreneurship</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
@@ -7774,7 +7774,7 @@
     <row r="119" ht="25.5" customHeight="1">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -7794,7 +7794,7 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>0506.40: Small Business and Entrepreneurship (TOP; verify)</t>
+          <t>Small Business and Entrepreneurship</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
@@ -7836,7 +7836,7 @@
     <row r="120" ht="25.5" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -7856,7 +7856,7 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>0506.40: Small Business and Entrepreneurship (TOP; verify)</t>
+          <t>Small Business and Entrepreneurship</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
@@ -7898,7 +7898,7 @@
     <row r="121" ht="25.5" customHeight="1">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -7960,7 +7960,7 @@
     <row r="122" ht="25.5" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -8022,7 +8022,7 @@
     <row r="123" ht="25.5" customHeight="1">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>0505.00: Business Administration (TOP; verify)</t>
+          <t>Business Administration</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
@@ -8084,7 +8084,7 @@
     <row r="124" ht="25.5" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -8146,7 +8146,7 @@
     <row r="125" ht="25.5" customHeight="1">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -8208,7 +8208,7 @@
     <row r="126" ht="25.5" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>0505.00: Business Administration (TOP; verify)</t>
+          <t>Business Administration</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
@@ -8270,7 +8270,7 @@
     <row r="127" ht="25.5" customHeight="1">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -8332,7 +8332,7 @@
     <row r="128" ht="25.5" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -8352,7 +8352,7 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>0505.00: Business Administration (TOP; verify)</t>
+          <t>Business Administration</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
@@ -8394,7 +8394,7 @@
     <row r="129" ht="25.5" customHeight="1">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>0505.00: Business Administration (TOP; verify)</t>
+          <t>Business Administration</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
@@ -8456,7 +8456,7 @@
     <row r="130" ht="25.5" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -8476,7 +8476,7 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>0505.00: Business Administration (TOP; verify)</t>
+          <t>Business Administration</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
@@ -8518,7 +8518,7 @@
     <row r="131" ht="25.5" customHeight="1">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>0610.00: Mass Communications (TOP; verify)</t>
+          <t>Mass Communications</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
@@ -8580,7 +8580,7 @@
     <row r="132" ht="25.5" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -8600,7 +8600,7 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>0614.00: Digital Media (TOP; verify)</t>
+          <t>Digital Media</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
@@ -8642,7 +8642,7 @@
     <row r="133" ht="25.5" customHeight="1">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>0709.10: E-Commerce (Technology emphasis) (TOP; verify)</t>
+          <t>E-Commerce (Technology emphasis)</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
@@ -8704,7 +8704,7 @@
     <row r="134" ht="25.5" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -8766,7 +8766,7 @@
     <row r="135" ht="25.5" customHeight="1">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -8828,7 +8828,7 @@
     <row r="136" ht="25.5" customHeight="1">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -8890,7 +8890,7 @@
     <row r="137" ht="25.5" customHeight="1">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>4930.12: Job Seeking/Changing Skills (TOP; verify)</t>
+          <t>Job Seeking/Changing Skills</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
@@ -8952,7 +8952,7 @@
     <row r="138" ht="25.5" customHeight="1">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -9014,7 +9014,7 @@
     <row r="139" ht="25.5" customHeight="1">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
@@ -9076,7 +9076,7 @@
     <row r="140" ht="25.5" customHeight="1">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -9138,7 +9138,7 @@
     <row r="141" ht="25.5" customHeight="1">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -9158,7 +9158,7 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
@@ -9200,7 +9200,7 @@
     <row r="142" ht="25.5" customHeight="1">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -9262,7 +9262,7 @@
     <row r="143" ht="25.5" customHeight="1">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -9324,7 +9324,7 @@
     <row r="144" ht="25.5" customHeight="1">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
@@ -9386,7 +9386,7 @@
     <row r="145" ht="25.5" customHeight="1">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
@@ -9406,7 +9406,7 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>0509.10: Advertising (TOP; verify)</t>
+          <t>Advertising</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
     <row r="146" ht="25.5" customHeight="1">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
@@ -9468,7 +9468,7 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>0509.10: Advertising (TOP; verify)</t>
+          <t>Advertising</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
@@ -9510,7 +9510,7 @@
     <row r="147" ht="25.5" customHeight="1">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
@@ -9572,7 +9572,7 @@
     <row r="148" ht="25.5" customHeight="1">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
@@ -9592,7 +9592,7 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>0509.10: Advertising (TOP; verify)</t>
+          <t>Advertising</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
@@ -9634,7 +9634,7 @@
     <row r="149" ht="25.5" customHeight="1">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
@@ -9654,7 +9654,7 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>0509.10: Advertising (TOP; verify)</t>
+          <t>Advertising</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
@@ -9696,7 +9696,7 @@
     <row r="150" ht="25.5" customHeight="1">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>0509.10: Advertising (TOP; verify)</t>
+          <t>Advertising</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
@@ -9758,7 +9758,7 @@
     <row r="151" ht="25.5" customHeight="1">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
@@ -9820,7 +9820,7 @@
     <row r="152" ht="25.5" customHeight="1">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
@@ -9882,7 +9882,7 @@
     <row r="153" ht="25.5" customHeight="1">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
@@ -9944,7 +9944,7 @@
     <row r="154" ht="25.5" customHeight="1">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
@@ -9964,7 +9964,7 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
@@ -10006,7 +10006,7 @@
     <row r="155" ht="25.5" customHeight="1">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
@@ -10068,7 +10068,7 @@
     <row r="156" ht="25.5" customHeight="1">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
@@ -10130,7 +10130,7 @@
     <row r="157" ht="25.5" customHeight="1">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
@@ -10192,7 +10192,7 @@
     <row r="158" ht="25.5" customHeight="1">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
@@ -10254,7 +10254,7 @@
     <row r="159" ht="25.5" customHeight="1">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
@@ -10316,7 +10316,7 @@
     <row r="160" ht="25.5" customHeight="1">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
@@ -10378,7 +10378,7 @@
     <row r="161" ht="25.5" customHeight="1">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
@@ -10440,7 +10440,7 @@
     <row r="162" ht="25.5" customHeight="1">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
@@ -10502,7 +10502,7 @@
     <row r="163" ht="25.5" customHeight="1">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
@@ -10564,7 +10564,7 @@
     <row r="164" ht="25.5" customHeight="1">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
@@ -10626,7 +10626,7 @@
     <row r="165" ht="25.5" customHeight="1">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
@@ -10688,7 +10688,7 @@
     <row r="166" ht="25.5" customHeight="1">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
@@ -10708,7 +10708,7 @@
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>1307.10: Restaurant and Food Services and Management (TOP; verify)</t>
+          <t>Restaurant and Food Services and Management</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
@@ -10750,7 +10750,7 @@
     <row r="167" ht="25.5" customHeight="1">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
@@ -10770,7 +10770,7 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>0509.10: Advertising (TOP; verify)</t>
+          <t>Advertising</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr">
@@ -10812,7 +10812,7 @@
     <row r="168" ht="25.5" customHeight="1">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
@@ -10832,7 +10832,7 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>0509.10: Advertising (TOP; verify)</t>
+          <t>Advertising</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr">
@@ -10874,7 +10874,7 @@
     <row r="169" ht="25.5" customHeight="1">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
@@ -10936,7 +10936,7 @@
     <row r="170" ht="25.5" customHeight="1">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
@@ -10956,7 +10956,7 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>0509.10: Advertising (TOP; verify)</t>
+          <t>Advertising</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
@@ -10998,7 +10998,7 @@
     <row r="171" ht="25.5" customHeight="1">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>0509.10: Advertising (TOP; verify)</t>
+          <t>Advertising</t>
         </is>
       </c>
       <c r="F171" s="2" t="inlineStr">
@@ -11060,7 +11060,7 @@
     <row r="172" ht="25.5" customHeight="1">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
@@ -11080,7 +11080,7 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>0509.10: Advertising (TOP; verify)</t>
+          <t>Advertising</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr">
@@ -11122,7 +11122,7 @@
     <row r="173" ht="25.5" customHeight="1">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
@@ -11142,7 +11142,7 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>0501.00: Business and Commerce, General (TOP; verify)</t>
+          <t>Business and Commerce, General</t>
         </is>
       </c>
       <c r="F173" s="2" t="inlineStr">
@@ -11184,7 +11184,7 @@
     <row r="174" ht="25.5" customHeight="1">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
@@ -11204,7 +11204,7 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr">
@@ -11246,7 +11246,7 @@
     <row r="175" ht="25.5" customHeight="1">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
@@ -11266,7 +11266,7 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>0509.10: Advertising (TOP; verify)</t>
+          <t>Advertising</t>
         </is>
       </c>
       <c r="F175" s="2" t="inlineStr">
@@ -11308,7 +11308,7 @@
     <row r="176" ht="25.5" customHeight="1">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
@@ -11328,7 +11328,7 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>0509.10: Advertising (TOP; verify)</t>
+          <t>Advertising</t>
         </is>
       </c>
       <c r="F176" s="2" t="inlineStr">
@@ -11370,7 +11370,7 @@
     <row r="177" ht="25.5" customHeight="1">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
@@ -11432,7 +11432,7 @@
     <row r="178" ht="25.5" customHeight="1">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
@@ -11494,7 +11494,7 @@
     <row r="179" ht="25.5" customHeight="1">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
@@ -11556,7 +11556,7 @@
     <row r="180" ht="25.5" customHeight="1">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
@@ -11576,7 +11576,7 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr">
@@ -11618,7 +11618,7 @@
     <row r="181" ht="25.5" customHeight="1">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
@@ -11680,7 +11680,7 @@
     <row r="182" ht="25.5" customHeight="1">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
@@ -11742,7 +11742,7 @@
     <row r="183" ht="25.5" customHeight="1">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
@@ -11762,7 +11762,7 @@
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F183" s="2" t="inlineStr">
@@ -11804,7 +11804,7 @@
     <row r="184" ht="25.5" customHeight="1">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr">
@@ -11866,7 +11866,7 @@
     <row r="185" ht="25.5" customHeight="1">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
@@ -11886,7 +11886,7 @@
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F185" s="2" t="inlineStr">
@@ -11928,7 +11928,7 @@
     <row r="186" ht="25.5" customHeight="1">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
@@ -11948,7 +11948,7 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>0509.10: Advertising (TOP; verify)</t>
+          <t>Advertising</t>
         </is>
       </c>
       <c r="F186" s="2" t="inlineStr">
@@ -11990,7 +11990,7 @@
     <row r="187" ht="25.5" customHeight="1">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
@@ -12010,7 +12010,7 @@
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>0509.10: Advertising (TOP; verify)</t>
+          <t>Advertising</t>
         </is>
       </c>
       <c r="F187" s="2" t="inlineStr">
@@ -12052,7 +12052,7 @@
     <row r="188" ht="25.5" customHeight="1">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
@@ -12072,7 +12072,7 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>0509.10: Advertising (TOP; verify)</t>
+          <t>Advertising</t>
         </is>
       </c>
       <c r="F188" s="2" t="inlineStr">
@@ -12114,7 +12114,7 @@
     <row r="189" ht="25.5" customHeight="1">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
@@ -12134,7 +12134,7 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>0509.10: Advertising (TOP; verify)</t>
+          <t>Advertising</t>
         </is>
       </c>
       <c r="F189" s="2" t="inlineStr">
@@ -12176,7 +12176,7 @@
     <row r="190" ht="25.5" customHeight="1">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
@@ -12238,7 +12238,7 @@
     <row r="191" ht="25.5" customHeight="1">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
@@ -12300,7 +12300,7 @@
     <row r="192" ht="25.5" customHeight="1">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
@@ -12320,7 +12320,7 @@
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>1030.00: Graphic Art and Design (TOP; verify)</t>
+          <t>Graphic Art and Design</t>
         </is>
       </c>
       <c r="F192" s="2" t="inlineStr">
@@ -12362,7 +12362,7 @@
     <row r="193" ht="25.5" customHeight="1">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
@@ -12424,7 +12424,7 @@
     <row r="194" ht="25.5" customHeight="1">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
@@ -12486,7 +12486,7 @@
     <row r="195" ht="25.5" customHeight="1">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
@@ -12506,7 +12506,7 @@
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>0604.00: Radio and Television (TOP; verify)</t>
+          <t>Radio and Television</t>
         </is>
       </c>
       <c r="F195" s="2" t="inlineStr">
@@ -12548,7 +12548,7 @@
     <row r="196" ht="25.5" customHeight="1">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
@@ -12568,7 +12568,7 @@
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>0509.10: Advertising (TOP; verify)</t>
+          <t>Advertising</t>
         </is>
       </c>
       <c r="F196" s="2" t="inlineStr">
@@ -12610,7 +12610,7 @@
     <row r="197" ht="25.5" customHeight="1">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F197" s="2" t="inlineStr">
@@ -12672,7 +12672,7 @@
     <row r="198" ht="25.5" customHeight="1">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
@@ -12734,7 +12734,7 @@
     <row r="199" ht="25.5" customHeight="1">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
@@ -12796,7 +12796,7 @@
     <row r="200" ht="25.5" customHeight="1">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
@@ -12858,7 +12858,7 @@
     <row r="201" ht="25.5" customHeight="1">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
@@ -12920,7 +12920,7 @@
     <row r="202" ht="25.5" customHeight="1">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
@@ -12982,7 +12982,7 @@
     <row r="203" ht="25.5" customHeight="1">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
@@ -13002,7 +13002,7 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F203" s="2" t="inlineStr">
@@ -13044,7 +13044,7 @@
     <row r="204" ht="25.5" customHeight="1">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F204" s="2" t="inlineStr">
@@ -13106,7 +13106,7 @@
     <row r="205" ht="25.5" customHeight="1">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
@@ -13168,7 +13168,7 @@
     <row r="206" ht="25.5" customHeight="1">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>1030.00: Graphic Art and Design (TOP; verify)</t>
+          <t>Graphic Art and Design</t>
         </is>
       </c>
       <c r="F206" s="2" t="inlineStr">
@@ -13230,7 +13230,7 @@
     <row r="207" ht="25.5" customHeight="1">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>1307.00: Hospitality (TOP; verify)</t>
+          <t>Hospitality</t>
         </is>
       </c>
       <c r="F207" s="2" t="inlineStr">
@@ -13292,7 +13292,7 @@
     <row r="208" ht="25.5" customHeight="1">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
@@ -13354,7 +13354,7 @@
     <row r="209" ht="25.5" customHeight="1">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
@@ -13416,7 +13416,7 @@
     <row r="210" ht="25.5" customHeight="1">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
@@ -13436,7 +13436,7 @@
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>0506.00: Business Management (TOP; verify)</t>
+          <t>Business Management</t>
         </is>
       </c>
       <c r="F210" s="2" t="inlineStr">
@@ -13478,7 +13478,7 @@
     <row r="211" ht="25.5" customHeight="1">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>0614.30: Website Design and Development (TOP; verify)</t>
+          <t>Website Design and Development</t>
         </is>
       </c>
       <c r="F211" s="2" t="inlineStr">
@@ -13540,7 +13540,7 @@
     <row r="212" ht="25.5" customHeight="1">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
@@ -13560,7 +13560,7 @@
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>0514.00: Office Technology/Office Computer Applications (TOP; verify)</t>
+          <t>Office Technology/Office Computer Applications</t>
         </is>
       </c>
       <c r="F212" s="2" t="inlineStr">
@@ -13602,7 +13602,7 @@
     <row r="213" ht="25.5" customHeight="1">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
@@ -13664,7 +13664,7 @@
     <row r="214" ht="25.5" customHeight="1">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
@@ -13726,7 +13726,7 @@
     <row r="215" ht="25.5" customHeight="1">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
@@ -13746,7 +13746,7 @@
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F215" s="2" t="inlineStr">
@@ -13788,7 +13788,7 @@
     <row r="216" ht="25.5" customHeight="1">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
@@ -13808,7 +13808,7 @@
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>0514.40: Office Management (TOP; verify)</t>
+          <t>Office Management</t>
         </is>
       </c>
       <c r="F216" s="2" t="inlineStr">
@@ -13850,7 +13850,7 @@
     <row r="217" ht="25.5" customHeight="1">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
@@ -13870,7 +13870,7 @@
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>0514.40: Office Management (TOP; verify)</t>
+          <t>Office Management</t>
         </is>
       </c>
       <c r="F217" s="2" t="inlineStr">
@@ -13912,7 +13912,7 @@
     <row r="218" ht="25.5" customHeight="1">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
@@ -13974,7 +13974,7 @@
     <row r="219" ht="25.5" customHeight="1">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
@@ -14036,7 +14036,7 @@
     <row r="220" ht="25.5" customHeight="1">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
@@ -14056,7 +14056,7 @@
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>0799.00: Other Information Technology (TOP; verify)</t>
+          <t>Other Information Technology</t>
         </is>
       </c>
       <c r="F220" s="2" t="inlineStr">
@@ -14098,7 +14098,7 @@
     <row r="221" ht="25.5" customHeight="1">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
@@ -14118,7 +14118,7 @@
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>0799.00: Other Information Technology (TOP; verify)</t>
+          <t>Other Information Technology</t>
         </is>
       </c>
       <c r="F221" s="2" t="inlineStr">
@@ -14160,7 +14160,7 @@
     <row r="222" ht="25.5" customHeight="1">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
@@ -14180,7 +14180,7 @@
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>0614.30: Website Design and Development (TOP; verify)</t>
+          <t>Website Design and Development</t>
         </is>
       </c>
       <c r="F222" s="2" t="inlineStr">
@@ -14222,7 +14222,7 @@
     <row r="223" ht="25.5" customHeight="1">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
@@ -14242,7 +14242,7 @@
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>0514.00: Office Technology/Office Computer Applications (TOP; verify)</t>
+          <t>Office Technology/Office Computer Applications</t>
         </is>
       </c>
       <c r="F223" s="2" t="inlineStr">
@@ -14284,7 +14284,7 @@
     <row r="224" ht="25.5" customHeight="1">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
@@ -14304,7 +14304,7 @@
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>0614.00: Digital Media (TOP; verify)</t>
+          <t>Digital Media</t>
         </is>
       </c>
       <c r="F224" s="2" t="inlineStr">
@@ -14346,7 +14346,7 @@
     <row r="225" ht="25.5" customHeight="1">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F225" s="2" t="inlineStr">
@@ -14408,7 +14408,7 @@
     <row r="226" ht="25.5" customHeight="1">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
@@ -14428,7 +14428,7 @@
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>0604.00: Radio and Television (TOP; verify)</t>
+          <t>Radio and Television</t>
         </is>
       </c>
       <c r="F226" s="2" t="inlineStr">
@@ -14470,7 +14470,7 @@
     <row r="227" ht="25.5" customHeight="1">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
@@ -14532,7 +14532,7 @@
     <row r="228" ht="25.5" customHeight="1">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
@@ -14594,7 +14594,7 @@
     <row r="229" ht="25.5" customHeight="1">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>0604.20: Television (including combined TV/Film/Video) (TOP; verify)</t>
+          <t>Television (including combined TV/Film/Video)</t>
         </is>
       </c>
       <c r="F229" s="2" t="inlineStr">
@@ -14656,7 +14656,7 @@
     <row r="230" ht="25.5" customHeight="1">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
@@ -14718,7 +14718,7 @@
     <row r="231" ht="25.5" customHeight="1">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
@@ -14738,7 +14738,7 @@
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>0506.40: Small Business and Entrepreneurship (TOP; verify)</t>
+          <t>Small Business and Entrepreneurship</t>
         </is>
       </c>
       <c r="F231" s="2" t="inlineStr">
@@ -14780,7 +14780,7 @@
     <row r="232" ht="25.5" customHeight="1">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
@@ -14800,7 +14800,7 @@
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F232" s="2" t="inlineStr">
@@ -14842,7 +14842,7 @@
     <row r="233" ht="25.5" customHeight="1">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
@@ -14862,7 +14862,7 @@
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>0701.00: Information Technology, General (TOP; verify)</t>
+          <t>Information Technology, General</t>
         </is>
       </c>
       <c r="F233" s="2" t="inlineStr">
@@ -14904,7 +14904,7 @@
     <row r="234" ht="25.5" customHeight="1">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F234" s="2" t="inlineStr">
@@ -14966,7 +14966,7 @@
     <row r="235" ht="25.5" customHeight="1">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
@@ -14986,7 +14986,7 @@
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>0509.10: Advertising (TOP; verify)</t>
+          <t>Advertising</t>
         </is>
       </c>
       <c r="F235" s="2" t="inlineStr">
@@ -15028,7 +15028,7 @@
     <row r="236" ht="25.5" customHeight="1">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
@@ -15090,7 +15090,7 @@
     <row r="237" ht="25.5" customHeight="1">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
@@ -15110,7 +15110,7 @@
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>0506.40: Small Business and Entrepreneurship (TOP; verify)</t>
+          <t>Small Business and Entrepreneurship</t>
         </is>
       </c>
       <c r="F237" s="2" t="inlineStr">
@@ -15152,7 +15152,7 @@
     <row r="238" ht="25.5" customHeight="1">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
@@ -15172,7 +15172,7 @@
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>0709.10: E-Commerce (Technology emphasis) (TOP; verify)</t>
+          <t>E-Commerce (Technology emphasis)</t>
         </is>
       </c>
       <c r="F238" s="2" t="inlineStr">
@@ -15214,7 +15214,7 @@
     <row r="239" ht="25.5" customHeight="1">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
@@ -15234,7 +15234,7 @@
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>0702.10: Software Applications (TOP; verify)</t>
+          <t>Software Applications</t>
         </is>
       </c>
       <c r="F239" s="2" t="inlineStr">
@@ -15276,7 +15276,7 @@
     <row r="240" ht="25.5" customHeight="1">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
@@ -15296,7 +15296,7 @@
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>0509.70: E-Commerce (Business emphasis) (TOP; verify)</t>
+          <t>E-Commerce (Business emphasis)</t>
         </is>
       </c>
       <c r="F240" s="2" t="inlineStr">
@@ -15338,7 +15338,7 @@
     <row r="241" ht="25.5" customHeight="1">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
@@ -15358,7 +15358,7 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>0509.70: E-Commerce (Business emphasis) (TOP; verify)</t>
+          <t>E-Commerce (Business emphasis)</t>
         </is>
       </c>
       <c r="F241" s="2" t="inlineStr">
@@ -15400,7 +15400,7 @@
     <row r="242" ht="25.5" customHeight="1">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
@@ -15420,7 +15420,7 @@
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>0614.00: Digital Media (TOP; verify)</t>
+          <t>Digital Media</t>
         </is>
       </c>
       <c r="F242" s="2" t="inlineStr">
@@ -15462,7 +15462,7 @@
     <row r="243" ht="25.5" customHeight="1">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
@@ -15482,7 +15482,7 @@
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>0511.00: Real Estate (TOP; verify)</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F243" s="2" t="inlineStr">
@@ -15524,7 +15524,7 @@
     <row r="244" ht="25.5" customHeight="1">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
@@ -15544,7 +15544,7 @@
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>0610.00: Mass Communications (TOP; verify)</t>
+          <t>Mass Communications</t>
         </is>
       </c>
       <c r="F244" s="2" t="inlineStr">
@@ -15586,7 +15586,7 @@
     <row r="245" ht="25.5" customHeight="1">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
@@ -15606,7 +15606,7 @@
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F245" s="2" t="inlineStr">
@@ -15648,7 +15648,7 @@
     <row r="246" ht="25.5" customHeight="1">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
@@ -15668,7 +15668,7 @@
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F246" s="2" t="inlineStr">
@@ -15710,7 +15710,7 @@
     <row r="247" ht="25.5" customHeight="1">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
@@ -15730,7 +15730,7 @@
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F247" s="2" t="inlineStr">
@@ -15772,7 +15772,7 @@
     <row r="248" ht="25.5" customHeight="1">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F248" s="2" t="inlineStr">
@@ -15834,7 +15834,7 @@
     <row r="249" ht="25.5" customHeight="1">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
@@ -15854,7 +15854,7 @@
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F249" s="2" t="inlineStr">
@@ -15896,7 +15896,7 @@
     <row r="250" ht="25.5" customHeight="1">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
@@ -15958,7 +15958,7 @@
     <row r="251" ht="25.5" customHeight="1">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
@@ -16020,7 +16020,7 @@
     <row r="252" ht="25.5" customHeight="1">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
@@ -16040,7 +16040,7 @@
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>0614.50: Desktop Publishing (TOP; verify)</t>
+          <t>Desktop Publishing</t>
         </is>
       </c>
       <c r="F252" s="2" t="inlineStr">
@@ -16082,7 +16082,7 @@
     <row r="253" ht="25.5" customHeight="1">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
@@ -16102,7 +16102,7 @@
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>0614.60: Computer Graphics and Digital Imagery (TOP; verify)</t>
+          <t>Computer Graphics and Digital Imagery</t>
         </is>
       </c>
       <c r="F253" s="2" t="inlineStr">
@@ -16144,7 +16144,7 @@
     <row r="254" ht="25.5" customHeight="1">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
@@ -16164,7 +16164,7 @@
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>0614.60: Computer Graphics and Digital Imagery (TOP; verify)</t>
+          <t>Computer Graphics and Digital Imagery</t>
         </is>
       </c>
       <c r="F254" s="2" t="inlineStr">
@@ -16206,7 +16206,7 @@
     <row r="255" ht="25.5" customHeight="1">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
@@ -16226,7 +16226,7 @@
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>0614.60: Computer Graphics and Digital Imagery (TOP; verify)</t>
+          <t>Computer Graphics and Digital Imagery</t>
         </is>
       </c>
       <c r="F255" s="2" t="inlineStr">
@@ -16268,7 +16268,7 @@
     <row r="256" ht="25.5" customHeight="1">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
@@ -16330,7 +16330,7 @@
     <row r="257" ht="25.5" customHeight="1">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
@@ -16392,7 +16392,7 @@
     <row r="258" ht="25.5" customHeight="1">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
@@ -16454,7 +16454,7 @@
     <row r="259" ht="25.5" customHeight="1">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
@@ -16516,7 +16516,7 @@
     <row r="260" ht="25.5" customHeight="1">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
@@ -16536,7 +16536,7 @@
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F260" s="2" t="inlineStr">
@@ -16578,7 +16578,7 @@
     <row r="261" ht="25.5" customHeight="1">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
@@ -16640,7 +16640,7 @@
     <row r="262" ht="25.5" customHeight="1">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
@@ -16702,7 +16702,7 @@
     <row r="263" ht="25.5" customHeight="1">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
@@ -16764,7 +16764,7 @@
     <row r="264" ht="25.5" customHeight="1">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
@@ -16826,7 +16826,7 @@
     <row r="265" ht="25.5" customHeight="1">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
@@ -16888,7 +16888,7 @@
     <row r="266" ht="25.5" customHeight="1">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
@@ -16908,7 +16908,7 @@
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F266" s="2" t="inlineStr">
@@ -16950,7 +16950,7 @@
     <row r="267" ht="25.5" customHeight="1">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
@@ -17012,7 +17012,7 @@
     <row r="268" ht="25.5" customHeight="1">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B268" s="2" t="inlineStr">
@@ -17074,7 +17074,7 @@
     <row r="269" ht="25.5" customHeight="1">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
@@ -17136,7 +17136,7 @@
     <row r="270" ht="25.5" customHeight="1">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
@@ -17156,7 +17156,7 @@
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>0514.00: Office Technology/Office Computer Applications (TOP; verify)</t>
+          <t>Office Technology/Office Computer Applications</t>
         </is>
       </c>
       <c r="F270" s="2" t="inlineStr">
@@ -17198,7 +17198,7 @@
     <row r="271" ht="25.5" customHeight="1">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
@@ -17260,7 +17260,7 @@
     <row r="272" ht="25.5" customHeight="1">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
@@ -17322,7 +17322,7 @@
     <row r="273" ht="25.5" customHeight="1">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
@@ -17384,7 +17384,7 @@
     <row r="274" ht="25.5" customHeight="1">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
@@ -17446,7 +17446,7 @@
     <row r="275" ht="25.5" customHeight="1">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
@@ -17466,7 +17466,7 @@
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>0614.30: Website Design and Development (TOP; verify)</t>
+          <t>Website Design and Development</t>
         </is>
       </c>
       <c r="F275" s="2" t="inlineStr">
@@ -17508,7 +17508,7 @@
     <row r="276" ht="25.5" customHeight="1">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
@@ -17528,7 +17528,7 @@
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>0614.30: Website Design and Development (TOP; verify)</t>
+          <t>Website Design and Development</t>
         </is>
       </c>
       <c r="F276" s="2" t="inlineStr">
@@ -17570,7 +17570,7 @@
     <row r="277" ht="25.5" customHeight="1">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B277" s="2" t="inlineStr">
@@ -17632,7 +17632,7 @@
     <row r="278" ht="25.5" customHeight="1">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
@@ -17652,7 +17652,7 @@
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>0501.00: Business and Commerce, General (TOP; verify)</t>
+          <t>Business and Commerce, General</t>
         </is>
       </c>
       <c r="F278" s="2" t="inlineStr">
@@ -17694,7 +17694,7 @@
     <row r="279" ht="25.5" customHeight="1">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B279" s="2" t="inlineStr">
@@ -17714,7 +17714,7 @@
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F279" s="2" t="inlineStr">
@@ -17756,7 +17756,7 @@
     <row r="280" ht="25.5" customHeight="1">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
@@ -17818,7 +17818,7 @@
     <row r="281" ht="25.5" customHeight="1">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
@@ -17880,7 +17880,7 @@
     <row r="282" ht="25.5" customHeight="1">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
@@ -17900,7 +17900,7 @@
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>0709.10: E-Commerce (Technology emphasis) (TOP; verify)</t>
+          <t>E-Commerce (Technology emphasis)</t>
         </is>
       </c>
       <c r="F282" s="2" t="inlineStr">
@@ -17942,7 +17942,7 @@
     <row r="283" ht="25.5" customHeight="1">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B283" s="2" t="inlineStr">
@@ -18004,7 +18004,7 @@
     <row r="284" ht="25.5" customHeight="1">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B284" s="2" t="inlineStr">
@@ -18024,7 +18024,7 @@
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>0509.70: E-Commerce (Business emphasis) (TOP; verify)</t>
+          <t>E-Commerce (Business emphasis)</t>
         </is>
       </c>
       <c r="F284" s="2" t="inlineStr">
@@ -18066,7 +18066,7 @@
     <row r="285" ht="25.5" customHeight="1">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B285" s="2" t="inlineStr">
@@ -18128,7 +18128,7 @@
     <row r="286" ht="25.5" customHeight="1">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B286" s="2" t="inlineStr">
@@ -18190,7 +18190,7 @@
     <row r="287" ht="25.5" customHeight="1">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B287" s="2" t="inlineStr">
@@ -18252,7 +18252,7 @@
     <row r="288" ht="25.5" customHeight="1">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B288" s="2" t="inlineStr">
@@ -18272,7 +18272,7 @@
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>0501.00: Business and Commerce, General (TOP; verify)</t>
+          <t>Business and Commerce, General</t>
         </is>
       </c>
       <c r="F288" s="2" t="inlineStr">
@@ -18314,7 +18314,7 @@
     <row r="289" ht="25.5" customHeight="1">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B289" s="2" t="inlineStr">
@@ -18334,7 +18334,7 @@
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>1303.20: Fashion Merchandising (TOP; verify)</t>
+          <t>Fashion Merchandising</t>
         </is>
       </c>
       <c r="F289" s="2" t="inlineStr">
@@ -18376,7 +18376,7 @@
     <row r="290" ht="25.5" customHeight="1">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B290" s="2" t="inlineStr">
@@ -18396,7 +18396,7 @@
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>0510.00: Logistics and Materials Transportation (TOP; verify)</t>
+          <t>Logistics and Materials Transportation</t>
         </is>
       </c>
       <c r="F290" s="2" t="inlineStr">
@@ -18438,7 +18438,7 @@
     <row r="291" ht="25.5" customHeight="1">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B291" s="2" t="inlineStr">
@@ -18500,7 +18500,7 @@
     <row r="292" ht="25.5" customHeight="1">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
@@ -18520,7 +18520,7 @@
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>1307.00: Hospitality (TOP; verify)</t>
+          <t>Hospitality</t>
         </is>
       </c>
       <c r="F292" s="2" t="inlineStr">
@@ -18562,7 +18562,7 @@
     <row r="293" ht="25.5" customHeight="1">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
@@ -18624,7 +18624,7 @@
     <row r="294" ht="25.5" customHeight="1">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
@@ -18686,7 +18686,7 @@
     <row r="295" ht="25.5" customHeight="1">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B295" s="2" t="inlineStr">
@@ -18748,7 +18748,7 @@
     <row r="296" ht="25.5" customHeight="1">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B296" s="2" t="inlineStr">
@@ -18810,7 +18810,7 @@
     <row r="297" ht="25.5" customHeight="1">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
@@ -18872,7 +18872,7 @@
     <row r="298" ht="25.5" customHeight="1">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
@@ -18892,7 +18892,7 @@
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>0709.10: E-Commerce (Technology emphasis) (TOP; verify)</t>
+          <t>E-Commerce (Technology emphasis)</t>
         </is>
       </c>
       <c r="F298" s="2" t="inlineStr">
@@ -18934,7 +18934,7 @@
     <row r="299" ht="25.5" customHeight="1">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
@@ -18996,7 +18996,7 @@
     <row r="300" ht="25.5" customHeight="1">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B300" s="2" t="inlineStr">
@@ -19016,7 +19016,7 @@
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>0709.10: E-Commerce (Technology emphasis) (TOP; verify)</t>
+          <t>E-Commerce (Technology emphasis)</t>
         </is>
       </c>
       <c r="F300" s="2" t="inlineStr">
@@ -19058,7 +19058,7 @@
     <row r="301" ht="25.5" customHeight="1">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
@@ -19078,7 +19078,7 @@
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>1303.20: Fashion Merchandising (TOP; verify)</t>
+          <t>Fashion Merchandising</t>
         </is>
       </c>
       <c r="F301" s="2" t="inlineStr">
@@ -19120,7 +19120,7 @@
     <row r="302" ht="25.5" customHeight="1">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B302" s="2" t="inlineStr">
@@ -19182,7 +19182,7 @@
     <row r="303" ht="25.5" customHeight="1">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B303" s="2" t="inlineStr">
@@ -19244,7 +19244,7 @@
     <row r="304" ht="25.5" customHeight="1">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B304" s="2" t="inlineStr">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>0709.10: E-Commerce (Technology emphasis) (TOP; verify)</t>
+          <t>E-Commerce (Technology emphasis)</t>
         </is>
       </c>
       <c r="F304" s="2" t="inlineStr">
@@ -19306,7 +19306,7 @@
     <row r="305" ht="25.5" customHeight="1">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B305" s="2" t="inlineStr">
@@ -19368,7 +19368,7 @@
     <row r="306" ht="25.5" customHeight="1">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B306" s="2" t="inlineStr">
@@ -19388,7 +19388,7 @@
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>0614.30: Website Design and Development (TOP; verify)</t>
+          <t>Website Design and Development</t>
         </is>
       </c>
       <c r="F306" s="2" t="inlineStr">
@@ -19430,7 +19430,7 @@
     <row r="307" ht="25.5" customHeight="1">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B307" s="2" t="inlineStr">
@@ -19492,7 +19492,7 @@
     <row r="308" ht="25.5" customHeight="1">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B308" s="2" t="inlineStr">
@@ -19554,7 +19554,7 @@
     <row r="309" ht="25.5" customHeight="1">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B309" s="2" t="inlineStr">
@@ -19574,7 +19574,7 @@
       </c>
       <c r="E309" s="2" t="inlineStr">
         <is>
-          <t>0509.70: E-Commerce (Business emphasis) (TOP; verify)</t>
+          <t>E-Commerce (Business emphasis)</t>
         </is>
       </c>
       <c r="F309" s="2" t="inlineStr">
@@ -19616,7 +19616,7 @@
     <row r="310" ht="25.5" customHeight="1">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B310" s="2" t="inlineStr">
@@ -19678,7 +19678,7 @@
     <row r="311" ht="25.5" customHeight="1">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B311" s="2" t="inlineStr">
@@ -19698,7 +19698,7 @@
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
-          <t>0506.00: Business Management (TOP; verify)</t>
+          <t>Business Management</t>
         </is>
       </c>
       <c r="F311" s="2" t="inlineStr">
@@ -19740,7 +19740,7 @@
     <row r="312" ht="25.5" customHeight="1">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B312" s="2" t="inlineStr">
@@ -19802,7 +19802,7 @@
     <row r="313" ht="25.5" customHeight="1">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B313" s="2" t="inlineStr">
@@ -19864,7 +19864,7 @@
     <row r="314" ht="25.5" customHeight="1">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B314" s="2" t="inlineStr">
@@ -19926,7 +19926,7 @@
     <row r="315" ht="25.5" customHeight="1">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B315" s="2" t="inlineStr">
@@ -19988,7 +19988,7 @@
     <row r="316" ht="25.5" customHeight="1">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B316" s="2" t="inlineStr">
@@ -20050,7 +20050,7 @@
     <row r="317" ht="25.5" customHeight="1">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B317" s="2" t="inlineStr">
@@ -20070,7 +20070,7 @@
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F317" s="2" t="inlineStr">
@@ -20112,7 +20112,7 @@
     <row r="318" ht="25.5" customHeight="1">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B318" s="2" t="inlineStr">
@@ -20132,7 +20132,7 @@
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F318" s="2" t="inlineStr">
@@ -20174,7 +20174,7 @@
     <row r="319" ht="25.5" customHeight="1">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B319" s="2" t="inlineStr">
@@ -20236,7 +20236,7 @@
     <row r="320" ht="25.5" customHeight="1">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B320" s="2" t="inlineStr">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F320" s="2" t="inlineStr">
@@ -20298,7 +20298,7 @@
     <row r="321" ht="25.5" customHeight="1">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B321" s="2" t="inlineStr">
@@ -20360,7 +20360,7 @@
     <row r="322" ht="25.5" customHeight="1">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B322" s="2" t="inlineStr">
@@ -20380,7 +20380,7 @@
       </c>
       <c r="E322" s="2" t="inlineStr">
         <is>
-          <t>0501.00: Business and Commerce, General (TOP; verify)</t>
+          <t>Business and Commerce, General</t>
         </is>
       </c>
       <c r="F322" s="2" t="inlineStr">
@@ -20422,7 +20422,7 @@
     <row r="323" ht="25.5" customHeight="1">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B323" s="2" t="inlineStr">
@@ -20442,7 +20442,7 @@
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F323" s="2" t="inlineStr">
@@ -20484,7 +20484,7 @@
     <row r="324" ht="25.5" customHeight="1">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B324" s="2" t="inlineStr">
@@ -20546,7 +20546,7 @@
     <row r="325" ht="25.5" customHeight="1">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B325" s="2" t="inlineStr">
@@ -20608,7 +20608,7 @@
     <row r="326" ht="25.5" customHeight="1">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B326" s="2" t="inlineStr">
@@ -20670,7 +20670,7 @@
     <row r="327" ht="25.5" customHeight="1">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B327" s="2" t="inlineStr">
@@ -20732,7 +20732,7 @@
     <row r="328" ht="25.5" customHeight="1">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B328" s="2" t="inlineStr">
@@ -20794,7 +20794,7 @@
     <row r="329" ht="25.5" customHeight="1">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B329" s="2" t="inlineStr">
@@ -20856,7 +20856,7 @@
     <row r="330" ht="25.5" customHeight="1">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B330" s="2" t="inlineStr">
@@ -20918,7 +20918,7 @@
     <row r="331" ht="25.5" customHeight="1">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B331" s="2" t="inlineStr">
@@ -20938,7 +20938,7 @@
       </c>
       <c r="E331" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F331" s="2" t="inlineStr">
@@ -20980,7 +20980,7 @@
     <row r="332" ht="25.5" customHeight="1">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B332" s="2" t="inlineStr">
@@ -21042,7 +21042,7 @@
     <row r="333" ht="25.5" customHeight="1">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B333" s="2" t="inlineStr">
@@ -21062,7 +21062,7 @@
       </c>
       <c r="E333" s="2" t="inlineStr">
         <is>
-          <t>0506.40: Small Business and Entrepreneurship (TOP; verify)</t>
+          <t>Small Business and Entrepreneurship</t>
         </is>
       </c>
       <c r="F333" s="2" t="inlineStr">
@@ -21104,7 +21104,7 @@
     <row r="334" ht="25.5" customHeight="1">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B334" s="2" t="inlineStr">
@@ -21166,7 +21166,7 @@
     <row r="335" ht="25.5" customHeight="1">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B335" s="2" t="inlineStr">
@@ -21228,7 +21228,7 @@
     <row r="336" ht="25.5" customHeight="1">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B336" s="2" t="inlineStr">
@@ -21290,7 +21290,7 @@
     <row r="337" ht="25.5" customHeight="1">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B337" s="2" t="inlineStr">
@@ -21310,7 +21310,7 @@
       </c>
       <c r="E337" s="2" t="inlineStr">
         <is>
-          <t>0508.00: International Business and Trade (TOP; verify)</t>
+          <t>International Business and Trade</t>
         </is>
       </c>
       <c r="F337" s="2" t="inlineStr">
@@ -21352,7 +21352,7 @@
     <row r="338" ht="25.5" customHeight="1">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B338" s="2" t="inlineStr">
@@ -21372,7 +21372,7 @@
       </c>
       <c r="E338" s="2" t="inlineStr">
         <is>
-          <t>0508.00: International Business and Trade (TOP; verify)</t>
+          <t>International Business and Trade</t>
         </is>
       </c>
       <c r="F338" s="2" t="inlineStr">
@@ -21414,7 +21414,7 @@
     <row r="339" ht="25.5" customHeight="1">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B339" s="2" t="inlineStr">
@@ -21476,7 +21476,7 @@
     <row r="340" ht="25.5" customHeight="1">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B340" s="2" t="inlineStr">
@@ -21538,7 +21538,7 @@
     <row r="341" ht="25.5" customHeight="1">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B341" s="2" t="inlineStr">
@@ -21558,7 +21558,7 @@
       </c>
       <c r="E341" s="2" t="inlineStr">
         <is>
-          <t>0501.00: Business and Commerce, General (TOP; verify)</t>
+          <t>Business and Commerce, General</t>
         </is>
       </c>
       <c r="F341" s="2" t="inlineStr">
@@ -21600,7 +21600,7 @@
     <row r="342" ht="25.5" customHeight="1">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B342" s="2" t="inlineStr">
@@ -21620,7 +21620,7 @@
       </c>
       <c r="E342" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F342" s="2" t="inlineStr">
@@ -21662,7 +21662,7 @@
     <row r="343" ht="25.5" customHeight="1">
       <c r="A343" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B343" s="2" t="inlineStr">
@@ -21682,7 +21682,7 @@
       </c>
       <c r="E343" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F343" s="2" t="inlineStr">
@@ -21724,7 +21724,7 @@
     <row r="344" ht="25.5" customHeight="1">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B344" s="2" t="inlineStr">
@@ -21786,7 +21786,7 @@
     <row r="345" ht="25.5" customHeight="1">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B345" s="2" t="inlineStr">
@@ -21848,7 +21848,7 @@
     <row r="346" ht="25.5" customHeight="1">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B346" s="2" t="inlineStr">
@@ -21910,7 +21910,7 @@
     <row r="347" ht="25.5" customHeight="1">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B347" s="2" t="inlineStr">
@@ -21972,7 +21972,7 @@
     <row r="348" ht="25.5" customHeight="1">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B348" s="2" t="inlineStr">
@@ -22034,7 +22034,7 @@
     <row r="349" ht="25.5" customHeight="1">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B349" s="2" t="inlineStr">
@@ -22054,7 +22054,7 @@
       </c>
       <c r="E349" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F349" s="2" t="inlineStr">
@@ -22096,7 +22096,7 @@
     <row r="350" ht="25.5" customHeight="1">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B350" s="2" t="inlineStr">
@@ -22116,7 +22116,7 @@
       </c>
       <c r="E350" s="2" t="inlineStr">
         <is>
-          <t>0506.40: Small Business and Entrepreneurship (TOP; verify)</t>
+          <t>Small Business and Entrepreneurship</t>
         </is>
       </c>
       <c r="F350" s="2" t="inlineStr">
@@ -22158,7 +22158,7 @@
     <row r="351" ht="25.5" customHeight="1">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B351" s="2" t="inlineStr">
@@ -22220,7 +22220,7 @@
     <row r="352" ht="25.5" customHeight="1">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B352" s="2" t="inlineStr">
@@ -22282,7 +22282,7 @@
     <row r="353" ht="25.5" customHeight="1">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B353" s="2" t="inlineStr">
@@ -22344,7 +22344,7 @@
     <row r="354" ht="25.5" customHeight="1">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B354" s="2" t="inlineStr">
@@ -22406,7 +22406,7 @@
     <row r="355" ht="25.5" customHeight="1">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B355" s="2" t="inlineStr">
@@ -22426,7 +22426,7 @@
       </c>
       <c r="E355" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F355" s="2" t="inlineStr">
@@ -22468,7 +22468,7 @@
     <row r="356" ht="25.5" customHeight="1">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B356" s="2" t="inlineStr">
@@ -22530,7 +22530,7 @@
     <row r="357" ht="25.5" customHeight="1">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B357" s="2" t="inlineStr">
@@ -22592,7 +22592,7 @@
     <row r="358" ht="25.5" customHeight="1">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B358" s="2" t="inlineStr">
@@ -22654,7 +22654,7 @@
     <row r="359" ht="25.5" customHeight="1">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B359" s="2" t="inlineStr">
@@ -22716,7 +22716,7 @@
     <row r="360" ht="25.5" customHeight="1">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B360" s="2" t="inlineStr">
@@ -22778,7 +22778,7 @@
     <row r="361" ht="25.5" customHeight="1">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B361" s="2" t="inlineStr">
@@ -22840,7 +22840,7 @@
     <row r="362" ht="25.5" customHeight="1">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B362" s="2" t="inlineStr">
@@ -22860,7 +22860,7 @@
       </c>
       <c r="E362" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F362" s="2" t="inlineStr">
@@ -22902,7 +22902,7 @@
     <row r="363" ht="25.5" customHeight="1">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B363" s="2" t="inlineStr">
@@ -22922,7 +22922,7 @@
       </c>
       <c r="E363" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F363" s="2" t="inlineStr">
@@ -22964,7 +22964,7 @@
     <row r="364" ht="25.5" customHeight="1">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B364" s="2" t="inlineStr">
@@ -22984,7 +22984,7 @@
       </c>
       <c r="E364" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F364" s="2" t="inlineStr">
@@ -23026,7 +23026,7 @@
     <row r="365" ht="25.5" customHeight="1">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B365" s="2" t="inlineStr">
@@ -23046,7 +23046,7 @@
       </c>
       <c r="E365" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F365" s="2" t="inlineStr">
@@ -23088,7 +23088,7 @@
     <row r="366" ht="25.5" customHeight="1">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B366" s="2" t="inlineStr">
@@ -23108,7 +23108,7 @@
       </c>
       <c r="E366" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F366" s="2" t="inlineStr">
@@ -23150,7 +23150,7 @@
     <row r="367" ht="25.5" customHeight="1">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B367" s="2" t="inlineStr">
@@ -23170,7 +23170,7 @@
       </c>
       <c r="E367" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F367" s="2" t="inlineStr">
@@ -23212,7 +23212,7 @@
     <row r="368" ht="25.5" customHeight="1">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B368" s="2" t="inlineStr">
@@ -23274,7 +23274,7 @@
     <row r="369" ht="25.5" customHeight="1">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B369" s="2" t="inlineStr">
@@ -23294,7 +23294,7 @@
       </c>
       <c r="E369" s="2" t="inlineStr">
         <is>
-          <t>0501.00: Business and Commerce, General (TOP; verify)</t>
+          <t>Business and Commerce, General</t>
         </is>
       </c>
       <c r="F369" s="2" t="inlineStr">
@@ -23336,7 +23336,7 @@
     <row r="370" ht="25.5" customHeight="1">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B370" s="2" t="inlineStr">
@@ -23356,7 +23356,7 @@
       </c>
       <c r="E370" s="2" t="inlineStr">
         <is>
-          <t>0506.40: Small Business and Entrepreneurship (TOP; verify)</t>
+          <t>Small Business and Entrepreneurship</t>
         </is>
       </c>
       <c r="F370" s="2" t="inlineStr">
@@ -23398,7 +23398,7 @@
     <row r="371" ht="25.5" customHeight="1">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B371" s="2" t="inlineStr">
@@ -23460,7 +23460,7 @@
     <row r="372" ht="25.5" customHeight="1">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B372" s="2" t="inlineStr">
@@ -23522,7 +23522,7 @@
     <row r="373" ht="25.5" customHeight="1">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B373" s="2" t="inlineStr">
@@ -23584,7 +23584,7 @@
     <row r="374" ht="25.5" customHeight="1">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B374" s="2" t="inlineStr">
@@ -23646,7 +23646,7 @@
     <row r="375" ht="25.5" customHeight="1">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B375" s="2" t="inlineStr">
@@ -23708,7 +23708,7 @@
     <row r="376" ht="25.5" customHeight="1">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B376" s="2" t="inlineStr">
@@ -23770,7 +23770,7 @@
     <row r="377" ht="25.5" customHeight="1">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B377" s="2" t="inlineStr">
@@ -23832,7 +23832,7 @@
     <row r="378" ht="25.5" customHeight="1">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B378" s="2" t="inlineStr">
@@ -23894,7 +23894,7 @@
     <row r="379" ht="25.5" customHeight="1">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B379" s="2" t="inlineStr">
@@ -23956,7 +23956,7 @@
     <row r="380" ht="25.5" customHeight="1">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B380" s="2" t="inlineStr">
@@ -24018,7 +24018,7 @@
     <row r="381" ht="25.5" customHeight="1">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B381" s="2" t="inlineStr">
@@ -24080,7 +24080,7 @@
     <row r="382" ht="25.5" customHeight="1">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B382" s="2" t="inlineStr">
@@ -24142,7 +24142,7 @@
     <row r="383" ht="25.5" customHeight="1">
       <c r="A383" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B383" s="2" t="inlineStr">
@@ -24162,7 +24162,7 @@
       </c>
       <c r="E383" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F383" s="2" t="inlineStr">
@@ -24204,7 +24204,7 @@
     <row r="384" ht="25.5" customHeight="1">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B384" s="2" t="inlineStr">
@@ -24224,7 +24224,7 @@
       </c>
       <c r="E384" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F384" s="2" t="inlineStr">
@@ -24266,7 +24266,7 @@
     <row r="385" ht="25.5" customHeight="1">
       <c r="A385" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B385" s="2" t="inlineStr">
@@ -24286,7 +24286,7 @@
       </c>
       <c r="E385" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F385" s="2" t="inlineStr">
@@ -24328,7 +24328,7 @@
     <row r="386" ht="25.5" customHeight="1">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B386" s="2" t="inlineStr">
@@ -24348,7 +24348,7 @@
       </c>
       <c r="E386" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F386" s="2" t="inlineStr">
@@ -24390,7 +24390,7 @@
     <row r="387" ht="25.5" customHeight="1">
       <c r="A387" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B387" s="2" t="inlineStr">
@@ -24410,7 +24410,7 @@
       </c>
       <c r="E387" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F387" s="2" t="inlineStr">
@@ -24452,7 +24452,7 @@
     <row r="388" ht="25.5" customHeight="1">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B388" s="2" t="inlineStr">
@@ -24472,7 +24472,7 @@
       </c>
       <c r="E388" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F388" s="2" t="inlineStr">
@@ -24514,7 +24514,7 @@
     <row r="389" ht="25.5" customHeight="1">
       <c r="A389" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B389" s="2" t="inlineStr">
@@ -24576,7 +24576,7 @@
     <row r="390" ht="25.5" customHeight="1">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B390" s="2" t="inlineStr">
@@ -24596,7 +24596,7 @@
       </c>
       <c r="E390" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F390" s="2" t="inlineStr">
@@ -24638,7 +24638,7 @@
     <row r="391" ht="25.5" customHeight="1">
       <c r="A391" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B391" s="2" t="inlineStr">
@@ -24658,7 +24658,7 @@
       </c>
       <c r="E391" s="2" t="inlineStr">
         <is>
-          <t>0501.00: Business and Commerce, General (TOP; verify)</t>
+          <t>Business and Commerce, General</t>
         </is>
       </c>
       <c r="F391" s="2" t="inlineStr">
@@ -24700,7 +24700,7 @@
     <row r="392" ht="25.5" customHeight="1">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B392" s="2" t="inlineStr">
@@ -24720,7 +24720,7 @@
       </c>
       <c r="E392" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F392" s="2" t="inlineStr">
@@ -24762,7 +24762,7 @@
     <row r="393" ht="25.5" customHeight="1">
       <c r="A393" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B393" s="2" t="inlineStr">
@@ -24782,7 +24782,7 @@
       </c>
       <c r="E393" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F393" s="2" t="inlineStr">
@@ -24824,7 +24824,7 @@
     <row r="394" ht="25.5" customHeight="1">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B394" s="2" t="inlineStr">
@@ -24844,7 +24844,7 @@
       </c>
       <c r="E394" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F394" s="2" t="inlineStr">
@@ -24886,7 +24886,7 @@
     <row r="395" ht="25.5" customHeight="1">
       <c r="A395" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B395" s="2" t="inlineStr">
@@ -24906,7 +24906,7 @@
       </c>
       <c r="E395" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F395" s="2" t="inlineStr">
@@ -24948,7 +24948,7 @@
     <row r="396" ht="25.5" customHeight="1">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B396" s="2" t="inlineStr">
@@ -25010,7 +25010,7 @@
     <row r="397" ht="25.5" customHeight="1">
       <c r="A397" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B397" s="2" t="inlineStr">
@@ -25030,7 +25030,7 @@
       </c>
       <c r="E397" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F397" s="2" t="inlineStr">
@@ -25072,7 +25072,7 @@
     <row r="398" ht="25.5" customHeight="1">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B398" s="2" t="inlineStr">
@@ -25134,7 +25134,7 @@
     <row r="399" ht="25.5" customHeight="1">
       <c r="A399" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B399" s="2" t="inlineStr">
@@ -25196,7 +25196,7 @@
     <row r="400" ht="25.5" customHeight="1">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B400" s="2" t="inlineStr">
@@ -25258,7 +25258,7 @@
     <row r="401" ht="25.5" customHeight="1">
       <c r="A401" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B401" s="2" t="inlineStr">
@@ -25278,7 +25278,7 @@
       </c>
       <c r="E401" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F401" s="2" t="inlineStr">
@@ -25320,7 +25320,7 @@
     <row r="402" ht="25.5" customHeight="1">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B402" s="2" t="inlineStr">
@@ -25382,7 +25382,7 @@
     <row r="403" ht="25.5" customHeight="1">
       <c r="A403" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B403" s="2" t="inlineStr">
@@ -25444,7 +25444,7 @@
     <row r="404" ht="25.5" customHeight="1">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B404" s="2" t="inlineStr">
@@ -25506,7 +25506,7 @@
     <row r="405" ht="25.5" customHeight="1">
       <c r="A405" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B405" s="2" t="inlineStr">
@@ -25568,7 +25568,7 @@
     <row r="406" ht="25.5" customHeight="1">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B406" s="2" t="inlineStr">
@@ -25630,7 +25630,7 @@
     <row r="407" ht="25.5" customHeight="1">
       <c r="A407" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B407" s="2" t="inlineStr">
@@ -25650,7 +25650,7 @@
       </c>
       <c r="E407" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F407" s="2" t="inlineStr">
@@ -25692,7 +25692,7 @@
     <row r="408" ht="25.5" customHeight="1">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B408" s="2" t="inlineStr">
@@ -25712,7 +25712,7 @@
       </c>
       <c r="E408" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F408" s="2" t="inlineStr">
@@ -25754,7 +25754,7 @@
     <row r="409" ht="25.5" customHeight="1">
       <c r="A409" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B409" s="2" t="inlineStr">
@@ -25774,7 +25774,7 @@
       </c>
       <c r="E409" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F409" s="2" t="inlineStr">
@@ -25816,7 +25816,7 @@
     <row r="410" ht="25.5" customHeight="1">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B410" s="2" t="inlineStr">
@@ -25836,7 +25836,7 @@
       </c>
       <c r="E410" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F410" s="2" t="inlineStr">
@@ -25878,7 +25878,7 @@
     <row r="411" ht="25.5" customHeight="1">
       <c r="A411" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B411" s="2" t="inlineStr">
@@ -25898,7 +25898,7 @@
       </c>
       <c r="E411" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F411" s="2" t="inlineStr">
@@ -25940,7 +25940,7 @@
     <row r="412" ht="25.5" customHeight="1">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B412" s="2" t="inlineStr">
@@ -25960,7 +25960,7 @@
       </c>
       <c r="E412" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F412" s="2" t="inlineStr">
@@ -26002,7 +26002,7 @@
     <row r="413" ht="25.5" customHeight="1">
       <c r="A413" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B413" s="2" t="inlineStr">
@@ -26022,7 +26022,7 @@
       </c>
       <c r="E413" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F413" s="2" t="inlineStr">
@@ -26064,7 +26064,7 @@
     <row r="414" ht="25.5" customHeight="1">
       <c r="A414" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B414" s="2" t="inlineStr">
@@ -26084,7 +26084,7 @@
       </c>
       <c r="E414" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F414" s="2" t="inlineStr">
@@ -26126,7 +26126,7 @@
     <row r="415" ht="25.5" customHeight="1">
       <c r="A415" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B415" s="2" t="inlineStr">
@@ -26146,7 +26146,7 @@
       </c>
       <c r="E415" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F415" s="2" t="inlineStr">
@@ -26188,7 +26188,7 @@
     <row r="416" ht="25.5" customHeight="1">
       <c r="A416" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B416" s="2" t="inlineStr">
@@ -26250,7 +26250,7 @@
     <row r="417" ht="25.5" customHeight="1">
       <c r="A417" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B417" s="2" t="inlineStr">
@@ -26270,7 +26270,7 @@
       </c>
       <c r="E417" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F417" s="2" t="inlineStr">
@@ -26312,7 +26312,7 @@
     <row r="418" ht="25.5" customHeight="1">
       <c r="A418" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B418" s="2" t="inlineStr">
@@ -26374,7 +26374,7 @@
     <row r="419" ht="25.5" customHeight="1">
       <c r="A419" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B419" s="2" t="inlineStr">
@@ -26436,7 +26436,7 @@
     <row r="420" ht="25.5" customHeight="1">
       <c r="A420" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B420" s="2" t="inlineStr">
@@ -26456,7 +26456,7 @@
       </c>
       <c r="E420" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F420" s="2" t="inlineStr">
@@ -26498,7 +26498,7 @@
     <row r="421" ht="25.5" customHeight="1">
       <c r="A421" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B421" s="2" t="inlineStr">
@@ -26560,7 +26560,7 @@
     <row r="422" ht="25.5" customHeight="1">
       <c r="A422" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B422" s="2" t="inlineStr">
@@ -26622,7 +26622,7 @@
     <row r="423" ht="25.5" customHeight="1">
       <c r="A423" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B423" s="2" t="inlineStr">
@@ -26642,7 +26642,7 @@
       </c>
       <c r="E423" s="2" t="inlineStr">
         <is>
-          <t>0506.00: Business Management (TOP; verify)</t>
+          <t>Business Management</t>
         </is>
       </c>
       <c r="F423" s="2" t="inlineStr">
@@ -26684,7 +26684,7 @@
     <row r="424" ht="25.5" customHeight="1">
       <c r="A424" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B424" s="2" t="inlineStr">
@@ -26704,7 +26704,7 @@
       </c>
       <c r="E424" s="2" t="inlineStr">
         <is>
-          <t>0506.00: Business Management (TOP; verify)</t>
+          <t>Business Management</t>
         </is>
       </c>
       <c r="F424" s="2" t="inlineStr">
@@ -26746,7 +26746,7 @@
     <row r="425" ht="25.5" customHeight="1">
       <c r="A425" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B425" s="2" t="inlineStr">
@@ -26808,7 +26808,7 @@
     <row r="426" ht="25.5" customHeight="1">
       <c r="A426" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B426" s="2" t="inlineStr">
@@ -26870,7 +26870,7 @@
     <row r="427" ht="25.5" customHeight="1">
       <c r="A427" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B427" s="2" t="inlineStr">
@@ -26932,7 +26932,7 @@
     <row r="428" ht="25.5" customHeight="1">
       <c r="A428" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B428" s="2" t="inlineStr">
@@ -26994,7 +26994,7 @@
     <row r="429" ht="25.5" customHeight="1">
       <c r="A429" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B429" s="2" t="inlineStr">
@@ -27056,7 +27056,7 @@
     <row r="430" ht="25.5" customHeight="1">
       <c r="A430" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B430" s="2" t="inlineStr">
@@ -27118,7 +27118,7 @@
     <row r="431" ht="25.5" customHeight="1">
       <c r="A431" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B431" s="2" t="inlineStr">
@@ -27180,7 +27180,7 @@
     <row r="432" ht="25.5" customHeight="1">
       <c r="A432" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B432" s="2" t="inlineStr">
@@ -27200,7 +27200,7 @@
       </c>
       <c r="E432" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F432" s="2" t="inlineStr">
@@ -27242,7 +27242,7 @@
     <row r="433" ht="25.5" customHeight="1">
       <c r="A433" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B433" s="2" t="inlineStr">
@@ -27262,7 +27262,7 @@
       </c>
       <c r="E433" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F433" s="2" t="inlineStr">
@@ -27304,7 +27304,7 @@
     <row r="434" ht="25.5" customHeight="1">
       <c r="A434" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B434" s="2" t="inlineStr">
@@ -27324,7 +27324,7 @@
       </c>
       <c r="E434" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F434" s="2" t="inlineStr">
@@ -27366,7 +27366,7 @@
     <row r="435" ht="25.5" customHeight="1">
       <c r="A435" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B435" s="2" t="inlineStr">
@@ -27428,7 +27428,7 @@
     <row r="436" ht="25.5" customHeight="1">
       <c r="A436" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B436" s="2" t="inlineStr">
@@ -27490,7 +27490,7 @@
     <row r="437" ht="25.5" customHeight="1">
       <c r="A437" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B437" s="2" t="inlineStr">
@@ -27552,7 +27552,7 @@
     <row r="438" ht="25.5" customHeight="1">
       <c r="A438" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B438" s="2" t="inlineStr">
@@ -27572,7 +27572,7 @@
       </c>
       <c r="E438" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F438" s="2" t="inlineStr">
@@ -27614,7 +27614,7 @@
     <row r="439" ht="25.5" customHeight="1">
       <c r="A439" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B439" s="2" t="inlineStr">
@@ -27634,7 +27634,7 @@
       </c>
       <c r="E439" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F439" s="2" t="inlineStr">
@@ -27676,7 +27676,7 @@
     <row r="440" ht="25.5" customHeight="1">
       <c r="A440" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B440" s="2" t="inlineStr">
@@ -27738,7 +27738,7 @@
     <row r="441" ht="25.5" customHeight="1">
       <c r="A441" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B441" s="2" t="inlineStr">
@@ -27800,7 +27800,7 @@
     <row r="442" ht="25.5" customHeight="1">
       <c r="A442" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B442" s="2" t="inlineStr">
@@ -27862,7 +27862,7 @@
     <row r="443" ht="25.5" customHeight="1">
       <c r="A443" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B443" s="2" t="inlineStr">
@@ -27924,7 +27924,7 @@
     <row r="444" ht="25.5" customHeight="1">
       <c r="A444" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B444" s="2" t="inlineStr">
@@ -27986,7 +27986,7 @@
     <row r="445" ht="25.5" customHeight="1">
       <c r="A445" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B445" s="2" t="inlineStr">
@@ -28048,7 +28048,7 @@
     <row r="446" ht="25.5" customHeight="1">
       <c r="A446" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B446" s="2" t="inlineStr">
@@ -28110,7 +28110,7 @@
     <row r="447" ht="25.5" customHeight="1">
       <c r="A447" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B447" s="2" t="inlineStr">
@@ -28172,7 +28172,7 @@
     <row r="448" ht="25.5" customHeight="1">
       <c r="A448" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B448" s="2" t="inlineStr">
@@ -28234,7 +28234,7 @@
     <row r="449" ht="25.5" customHeight="1">
       <c r="A449" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B449" s="2" t="inlineStr">
@@ -28296,7 +28296,7 @@
     <row r="450" ht="25.5" customHeight="1">
       <c r="A450" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B450" s="2" t="inlineStr">
@@ -28316,7 +28316,7 @@
       </c>
       <c r="E450" s="2" t="inlineStr">
         <is>
-          <t>0514.00: Office Technology/Office Computer Applications (TOP; verify)</t>
+          <t>Office Technology/Office Computer Applications</t>
         </is>
       </c>
       <c r="F450" s="2" t="inlineStr">
@@ -28358,7 +28358,7 @@
     <row r="451" ht="25.5" customHeight="1">
       <c r="A451" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B451" s="2" t="inlineStr">
@@ -28378,7 +28378,7 @@
       </c>
       <c r="E451" s="2" t="inlineStr">
         <is>
-          <t>0506.40: Small Business and Entrepreneurship (TOP; verify)</t>
+          <t>Small Business and Entrepreneurship</t>
         </is>
       </c>
       <c r="F451" s="2" t="inlineStr">
@@ -28420,7 +28420,7 @@
     <row r="452" ht="25.5" customHeight="1">
       <c r="A452" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B452" s="2" t="inlineStr">
@@ -28440,7 +28440,7 @@
       </c>
       <c r="E452" s="2" t="inlineStr">
         <is>
-          <t>0614.30: Website Design and Development (TOP; verify)</t>
+          <t>Website Design and Development</t>
         </is>
       </c>
       <c r="F452" s="2" t="inlineStr">
@@ -28482,7 +28482,7 @@
     <row r="453" ht="25.5" customHeight="1">
       <c r="A453" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B453" s="2" t="inlineStr">
@@ -28544,7 +28544,7 @@
     <row r="454" ht="25.5" customHeight="1">
       <c r="A454" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B454" s="2" t="inlineStr">
@@ -28606,7 +28606,7 @@
     <row r="455" ht="25.5" customHeight="1">
       <c r="A455" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B455" s="2" t="inlineStr">
@@ -28626,7 +28626,7 @@
       </c>
       <c r="E455" s="2" t="inlineStr">
         <is>
-          <t>0702.00: Computer Information Systems (TOP; verify)</t>
+          <t>Computer Information Systems</t>
         </is>
       </c>
       <c r="F455" s="2" t="inlineStr">
@@ -28668,7 +28668,7 @@
     <row r="456" ht="25.5" customHeight="1">
       <c r="A456" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B456" s="2" t="inlineStr">
@@ -28730,7 +28730,7 @@
     <row r="457" ht="25.5" customHeight="1">
       <c r="A457" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B457" s="2" t="inlineStr">
@@ -28750,7 +28750,7 @@
       </c>
       <c r="E457" s="2" t="inlineStr">
         <is>
-          <t>0614.30: Website Design and Development (TOP; verify)</t>
+          <t>Website Design and Development</t>
         </is>
       </c>
       <c r="F457" s="2" t="inlineStr">
@@ -28792,7 +28792,7 @@
     <row r="458" ht="25.5" customHeight="1">
       <c r="A458" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B458" s="2" t="inlineStr">
@@ -28812,7 +28812,7 @@
       </c>
       <c r="E458" s="2" t="inlineStr">
         <is>
-          <t>0709.00: World Wide Web Administration (TOP; verify)</t>
+          <t>World Wide Web Administration</t>
         </is>
       </c>
       <c r="F458" s="2" t="inlineStr">
@@ -28854,7 +28854,7 @@
     <row r="459" ht="25.5" customHeight="1">
       <c r="A459" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B459" s="2" t="inlineStr">
@@ -28916,7 +28916,7 @@
     <row r="460" ht="25.5" customHeight="1">
       <c r="A460" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B460" s="2" t="inlineStr">
@@ -28936,7 +28936,7 @@
       </c>
       <c r="E460" s="2" t="inlineStr">
         <is>
-          <t>0614.30: Website Design and Development (TOP; verify)</t>
+          <t>Website Design and Development</t>
         </is>
       </c>
       <c r="F460" s="2" t="inlineStr">
@@ -28978,7 +28978,7 @@
     <row r="461" ht="25.5" customHeight="1">
       <c r="A461" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B461" s="2" t="inlineStr">
@@ -28998,7 +28998,7 @@
       </c>
       <c r="E461" s="2" t="inlineStr">
         <is>
-          <t>0709.10: E-Commerce (Technology emphasis) (TOP; verify)</t>
+          <t>E-Commerce (Technology emphasis)</t>
         </is>
       </c>
       <c r="F461" s="2" t="inlineStr">
@@ -29040,7 +29040,7 @@
     <row r="462" ht="25.5" customHeight="1">
       <c r="A462" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B462" s="2" t="inlineStr">
@@ -29060,7 +29060,7 @@
       </c>
       <c r="E462" s="2" t="inlineStr">
         <is>
-          <t>0506.40: Small Business and Entrepreneurship (TOP; verify)</t>
+          <t>Small Business and Entrepreneurship</t>
         </is>
       </c>
       <c r="F462" s="2" t="inlineStr">
@@ -29102,7 +29102,7 @@
     <row r="463" ht="25.5" customHeight="1">
       <c r="A463" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B463" s="2" t="inlineStr">
@@ -29164,7 +29164,7 @@
     <row r="464" ht="25.5" customHeight="1">
       <c r="A464" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B464" s="2" t="inlineStr">
@@ -29184,7 +29184,7 @@
       </c>
       <c r="E464" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F464" s="2" t="inlineStr">
@@ -29226,7 +29226,7 @@
     <row r="465" ht="25.5" customHeight="1">
       <c r="A465" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B465" s="2" t="inlineStr">
@@ -29246,7 +29246,7 @@
       </c>
       <c r="E465" s="2" t="inlineStr">
         <is>
-          <t>0614.30: Website Design and Development (TOP; verify)</t>
+          <t>Website Design and Development</t>
         </is>
       </c>
       <c r="F465" s="2" t="inlineStr">
@@ -29288,7 +29288,7 @@
     <row r="466" ht="25.5" customHeight="1">
       <c r="A466" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B466" s="2" t="inlineStr">
@@ -29350,7 +29350,7 @@
     <row r="467" ht="25.5" customHeight="1">
       <c r="A467" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B467" s="2" t="inlineStr">
@@ -29412,7 +29412,7 @@
     <row r="468" ht="25.5" customHeight="1">
       <c r="A468" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B468" s="2" t="inlineStr">
@@ -29474,7 +29474,7 @@
     <row r="469" ht="25.5" customHeight="1">
       <c r="A469" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B469" s="2" t="inlineStr">
@@ -29536,7 +29536,7 @@
     <row r="470" ht="25.5" customHeight="1">
       <c r="A470" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B470" s="2" t="inlineStr">
@@ -29556,7 +29556,7 @@
       </c>
       <c r="E470" s="2" t="inlineStr">
         <is>
-          <t>0612.20: Film Production (TOP; verify)</t>
+          <t>Film Production</t>
         </is>
       </c>
       <c r="F470" s="2" t="inlineStr">
@@ -29598,7 +29598,7 @@
     <row r="471" ht="25.5" customHeight="1">
       <c r="A471" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B471" s="2" t="inlineStr">
@@ -29660,7 +29660,7 @@
     <row r="472" ht="25.5" customHeight="1">
       <c r="A472" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B472" s="2" t="inlineStr">
@@ -29722,7 +29722,7 @@
     <row r="473" ht="25.5" customHeight="1">
       <c r="A473" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B473" s="2" t="inlineStr">
@@ -29784,7 +29784,7 @@
     <row r="474" ht="25.5" customHeight="1">
       <c r="A474" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B474" s="2" t="inlineStr">
@@ -29846,7 +29846,7 @@
     <row r="475" ht="25.5" customHeight="1">
       <c r="A475" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B475" s="2" t="inlineStr">
@@ -29866,7 +29866,7 @@
       </c>
       <c r="E475" s="2" t="inlineStr">
         <is>
-          <t>0614.00: Digital Media (TOP; verify)</t>
+          <t>Digital Media</t>
         </is>
       </c>
       <c r="F475" s="2" t="inlineStr">
@@ -29908,7 +29908,7 @@
     <row r="476" ht="25.5" customHeight="1">
       <c r="A476" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B476" s="2" t="inlineStr">
@@ -29970,7 +29970,7 @@
     <row r="477" ht="25.5" customHeight="1">
       <c r="A477" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B477" s="2" t="inlineStr">
@@ -30032,7 +30032,7 @@
     <row r="478" ht="25.5" customHeight="1">
       <c r="A478" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B478" s="2" t="inlineStr">
@@ -30052,7 +30052,7 @@
       </c>
       <c r="E478" s="2" t="inlineStr">
         <is>
-          <t>0509.70: E-Commerce (Business emphasis) (TOP; verify)</t>
+          <t>E-Commerce (Business emphasis)</t>
         </is>
       </c>
       <c r="F478" s="2" t="inlineStr">
@@ -30094,7 +30094,7 @@
     <row r="479" ht="25.5" customHeight="1">
       <c r="A479" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B479" s="2" t="inlineStr">
@@ -30156,7 +30156,7 @@
     <row r="480" ht="25.5" customHeight="1">
       <c r="A480" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B480" s="2" t="inlineStr">
@@ -30176,7 +30176,7 @@
       </c>
       <c r="E480" s="2" t="inlineStr">
         <is>
-          <t>0701.00: Information Technology, General (TOP; verify)</t>
+          <t>Information Technology, General</t>
         </is>
       </c>
       <c r="F480" s="2" t="inlineStr">
@@ -30218,7 +30218,7 @@
     <row r="481" ht="25.5" customHeight="1">
       <c r="A481" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B481" s="2" t="inlineStr">
@@ -30238,7 +30238,7 @@
       </c>
       <c r="E481" s="2" t="inlineStr">
         <is>
-          <t>0701.00: Information Technology, General (TOP; verify)</t>
+          <t>Information Technology, General</t>
         </is>
       </c>
       <c r="F481" s="2" t="inlineStr">
@@ -30280,7 +30280,7 @@
     <row r="482" ht="25.5" customHeight="1">
       <c r="A482" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B482" s="2" t="inlineStr">
@@ -30300,7 +30300,7 @@
       </c>
       <c r="E482" s="2" t="inlineStr">
         <is>
-          <t>0701.00: Information Technology, General (TOP; verify)</t>
+          <t>Information Technology, General</t>
         </is>
       </c>
       <c r="F482" s="2" t="inlineStr">
@@ -30342,7 +30342,7 @@
     <row r="483" ht="25.5" customHeight="1">
       <c r="A483" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B483" s="2" t="inlineStr">
@@ -30404,7 +30404,7 @@
     <row r="484" ht="25.5" customHeight="1">
       <c r="A484" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B484" s="2" t="inlineStr">
@@ -30466,7 +30466,7 @@
     <row r="485" ht="25.5" customHeight="1">
       <c r="A485" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B485" s="2" t="inlineStr">
@@ -30486,7 +30486,7 @@
       </c>
       <c r="E485" s="2" t="inlineStr">
         <is>
-          <t>0614.30: Website Design and Development (TOP; verify)</t>
+          <t>Website Design and Development</t>
         </is>
       </c>
       <c r="F485" s="2" t="inlineStr">
@@ -30528,7 +30528,7 @@
     <row r="486" ht="25.5" customHeight="1">
       <c r="A486" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B486" s="2" t="inlineStr">
@@ -30548,7 +30548,7 @@
       </c>
       <c r="E486" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F486" s="2" t="inlineStr">
@@ -30590,7 +30590,7 @@
     <row r="487" ht="25.5" customHeight="1">
       <c r="A487" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B487" s="2" t="inlineStr">
@@ -30610,7 +30610,7 @@
       </c>
       <c r="E487" s="2" t="inlineStr">
         <is>
-          <t>0614.00: Digital Media (TOP; verify)</t>
+          <t>Digital Media</t>
         </is>
       </c>
       <c r="F487" s="2" t="inlineStr">
@@ -30652,7 +30652,7 @@
     <row r="488" ht="25.5" customHeight="1">
       <c r="A488" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B488" s="2" t="inlineStr">
@@ -30672,7 +30672,7 @@
       </c>
       <c r="E488" s="2" t="inlineStr">
         <is>
-          <t>0614.60: Computer Graphics and Digital Imagery (TOP; verify)</t>
+          <t>Computer Graphics and Digital Imagery</t>
         </is>
       </c>
       <c r="F488" s="2" t="inlineStr">
@@ -30714,7 +30714,7 @@
     <row r="489" ht="25.5" customHeight="1">
       <c r="A489" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B489" s="2" t="inlineStr">
@@ -30734,7 +30734,7 @@
       </c>
       <c r="E489" s="2" t="inlineStr">
         <is>
-          <t>0514.00: Office Technology/Office Computer Applications (TOP; verify)</t>
+          <t>Office Technology/Office Computer Applications</t>
         </is>
       </c>
       <c r="F489" s="2" t="inlineStr">
@@ -30776,7 +30776,7 @@
     <row r="490" ht="25.5" customHeight="1">
       <c r="A490" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B490" s="2" t="inlineStr">
@@ -30796,7 +30796,7 @@
       </c>
       <c r="E490" s="2" t="inlineStr">
         <is>
-          <t>0508.00: International Business and Trade (TOP; verify)</t>
+          <t>International Business and Trade</t>
         </is>
       </c>
       <c r="F490" s="2" t="inlineStr">
@@ -30838,7 +30838,7 @@
     <row r="491" ht="25.5" customHeight="1">
       <c r="A491" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B491" s="2" t="inlineStr">
@@ -30858,7 +30858,7 @@
       </c>
       <c r="E491" s="2" t="inlineStr">
         <is>
-          <t>0610.00: Mass Communications (TOP; verify)</t>
+          <t>Mass Communications</t>
         </is>
       </c>
       <c r="F491" s="2" t="inlineStr">
@@ -30900,7 +30900,7 @@
     <row r="492" ht="25.5" customHeight="1">
       <c r="A492" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B492" s="2" t="inlineStr">
@@ -30920,7 +30920,7 @@
       </c>
       <c r="E492" s="2" t="inlineStr">
         <is>
-          <t>0610.00: Mass Communications (TOP; verify)</t>
+          <t>Mass Communications</t>
         </is>
       </c>
       <c r="F492" s="2" t="inlineStr">
@@ -30962,7 +30962,7 @@
     <row r="493" ht="25.5" customHeight="1">
       <c r="A493" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B493" s="2" t="inlineStr">
@@ -30982,7 +30982,7 @@
       </c>
       <c r="E493" s="2" t="inlineStr">
         <is>
-          <t>0610.00: Mass Communications (TOP; verify)</t>
+          <t>Mass Communications</t>
         </is>
       </c>
       <c r="F493" s="2" t="inlineStr">
@@ -31024,7 +31024,7 @@
     <row r="494" ht="25.5" customHeight="1">
       <c r="A494" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B494" s="2" t="inlineStr">
@@ -31044,7 +31044,7 @@
       </c>
       <c r="E494" s="2" t="inlineStr">
         <is>
-          <t>0610.00: Mass Communications (TOP; verify)</t>
+          <t>Mass Communications</t>
         </is>
       </c>
       <c r="F494" s="2" t="inlineStr">
@@ -31086,7 +31086,7 @@
     <row r="495" ht="25.5" customHeight="1">
       <c r="A495" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B495" s="2" t="inlineStr">
@@ -31106,7 +31106,7 @@
       </c>
       <c r="E495" s="2" t="inlineStr">
         <is>
-          <t>0505.00: Business Administration (TOP; verify)</t>
+          <t>Business Administration</t>
         </is>
       </c>
       <c r="F495" s="2" t="inlineStr">
@@ -31148,7 +31148,7 @@
     <row r="496" ht="25.5" customHeight="1">
       <c r="A496" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B496" s="2" t="inlineStr">
@@ -31168,7 +31168,7 @@
       </c>
       <c r="E496" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F496" s="2" t="inlineStr">
@@ -31210,7 +31210,7 @@
     <row r="497" ht="25.5" customHeight="1">
       <c r="A497" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B497" s="2" t="inlineStr">
@@ -31230,7 +31230,7 @@
       </c>
       <c r="E497" s="2" t="inlineStr">
         <is>
-          <t>0702.10: Software Applications (TOP; verify)</t>
+          <t>Software Applications</t>
         </is>
       </c>
       <c r="F497" s="2" t="inlineStr">
@@ -31272,7 +31272,7 @@
     <row r="498" ht="25.5" customHeight="1">
       <c r="A498" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B498" s="2" t="inlineStr">
@@ -31292,7 +31292,7 @@
       </c>
       <c r="E498" s="2" t="inlineStr">
         <is>
-          <t>0614.10: Multimedia (TOP; verify)</t>
+          <t>Multimedia</t>
         </is>
       </c>
       <c r="F498" s="2" t="inlineStr">
@@ -31334,7 +31334,7 @@
     <row r="499" ht="25.5" customHeight="1">
       <c r="A499" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B499" s="2" t="inlineStr">
@@ -31354,7 +31354,7 @@
       </c>
       <c r="E499" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F499" s="2" t="inlineStr">
@@ -31396,7 +31396,7 @@
     <row r="500" ht="25.5" customHeight="1">
       <c r="A500" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B500" s="2" t="inlineStr">
@@ -31458,7 +31458,7 @@
     <row r="501" ht="25.5" customHeight="1">
       <c r="A501" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B501" s="2" t="inlineStr">
@@ -31478,7 +31478,7 @@
       </c>
       <c r="E501" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F501" s="2" t="inlineStr">
@@ -31520,7 +31520,7 @@
     <row r="502" ht="25.5" customHeight="1">
       <c r="A502" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B502" s="2" t="inlineStr">
@@ -31540,7 +31540,7 @@
       </c>
       <c r="E502" s="2" t="inlineStr">
         <is>
-          <t>0614.60: Computer Graphics and Digital Imagery (TOP; verify)</t>
+          <t>Computer Graphics and Digital Imagery</t>
         </is>
       </c>
       <c r="F502" s="2" t="inlineStr">
@@ -31582,7 +31582,7 @@
     <row r="503" ht="25.5" customHeight="1">
       <c r="A503" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B503" s="2" t="inlineStr">
@@ -31602,7 +31602,7 @@
       </c>
       <c r="E503" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F503" s="2" t="inlineStr">
@@ -31644,7 +31644,7 @@
     <row r="504" ht="25.5" customHeight="1">
       <c r="A504" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B504" s="2" t="inlineStr">
@@ -31664,7 +31664,7 @@
       </c>
       <c r="E504" s="2" t="inlineStr">
         <is>
-          <t>0614.30: Website Design and Development (TOP; verify)</t>
+          <t>Website Design and Development</t>
         </is>
       </c>
       <c r="F504" s="2" t="inlineStr">
@@ -31706,7 +31706,7 @@
     <row r="505" ht="25.5" customHeight="1">
       <c r="A505" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B505" s="2" t="inlineStr">
@@ -31768,7 +31768,7 @@
     <row r="506" ht="25.5" customHeight="1">
       <c r="A506" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B506" s="2" t="inlineStr">
@@ -31830,7 +31830,7 @@
     <row r="507" ht="25.5" customHeight="1">
       <c r="A507" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B507" s="2" t="inlineStr">
@@ -31850,7 +31850,7 @@
       </c>
       <c r="E507" s="2" t="inlineStr">
         <is>
-          <t>0699.00: Other Media and Communications (TOP; verify)</t>
+          <t>Other Media and Communications</t>
         </is>
       </c>
       <c r="F507" s="2" t="inlineStr">
@@ -31892,7 +31892,7 @@
     <row r="508" ht="25.5" customHeight="1">
       <c r="A508" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B508" s="2" t="inlineStr">
@@ -31912,7 +31912,7 @@
       </c>
       <c r="E508" s="2" t="inlineStr">
         <is>
-          <t>0614.10: Multimedia (TOP; verify)</t>
+          <t>Multimedia</t>
         </is>
       </c>
       <c r="F508" s="2" t="inlineStr">
@@ -31954,7 +31954,7 @@
     <row r="509" ht="25.5" customHeight="1">
       <c r="A509" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B509" s="2" t="inlineStr">
@@ -31974,7 +31974,7 @@
       </c>
       <c r="E509" s="2" t="inlineStr">
         <is>
-          <t>0699.00: Other Media and Communications (TOP; verify)</t>
+          <t>Other Media and Communications</t>
         </is>
       </c>
       <c r="F509" s="2" t="inlineStr">
@@ -32016,7 +32016,7 @@
     <row r="510" ht="25.5" customHeight="1">
       <c r="A510" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B510" s="2" t="inlineStr">
@@ -32078,7 +32078,7 @@
     <row r="511" ht="25.5" customHeight="1">
       <c r="A511" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B511" s="2" t="inlineStr">
@@ -32140,7 +32140,7 @@
     <row r="512" ht="25.5" customHeight="1">
       <c r="A512" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B512" s="2" t="inlineStr">
@@ -32202,7 +32202,7 @@
     <row r="513" ht="25.5" customHeight="1">
       <c r="A513" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B513" s="2" t="inlineStr">
@@ -32264,7 +32264,7 @@
     <row r="514" ht="25.5" customHeight="1">
       <c r="A514" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B514" s="2" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="E514" s="2" t="inlineStr">
         <is>
-          <t>0514.00: Office Technology/Office Computer Applications (TOP; verify)</t>
+          <t>Office Technology/Office Computer Applications</t>
         </is>
       </c>
       <c r="F514" s="2" t="inlineStr">
@@ -32326,7 +32326,7 @@
     <row r="515" ht="25.5" customHeight="1">
       <c r="A515" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B515" s="2" t="inlineStr">
@@ -32346,7 +32346,7 @@
       </c>
       <c r="E515" s="2" t="inlineStr">
         <is>
-          <t>0514.00: Office Technology/Office Computer Applications (TOP; verify)</t>
+          <t>Office Technology/Office Computer Applications</t>
         </is>
       </c>
       <c r="F515" s="2" t="inlineStr">
@@ -32388,7 +32388,7 @@
     <row r="516" ht="25.5" customHeight="1">
       <c r="A516" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B516" s="2" t="inlineStr">
@@ -32408,7 +32408,7 @@
       </c>
       <c r="E516" s="2" t="inlineStr">
         <is>
-          <t>0501.00: Business and Commerce, General (TOP; verify)</t>
+          <t>Business and Commerce, General</t>
         </is>
       </c>
       <c r="F516" s="2" t="inlineStr">
@@ -32450,7 +32450,7 @@
     <row r="517" ht="25.5" customHeight="1">
       <c r="A517" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B517" s="2" t="inlineStr">
@@ -32470,7 +32470,7 @@
       </c>
       <c r="E517" s="2" t="inlineStr">
         <is>
-          <t>0602.00: Journalism (TOP; verify)</t>
+          <t>Journalism</t>
         </is>
       </c>
       <c r="F517" s="2" t="inlineStr">
@@ -32512,7 +32512,7 @@
     <row r="518" ht="25.5" customHeight="1">
       <c r="A518" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B518" s="2" t="inlineStr">
@@ -32532,7 +32532,7 @@
       </c>
       <c r="E518" s="2" t="inlineStr">
         <is>
-          <t>0602.00: Journalism (TOP; verify)</t>
+          <t>Journalism</t>
         </is>
       </c>
       <c r="F518" s="2" t="inlineStr">
@@ -32574,7 +32574,7 @@
     <row r="519" ht="25.5" customHeight="1">
       <c r="A519" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B519" s="2" t="inlineStr">
@@ -32594,7 +32594,7 @@
       </c>
       <c r="E519" s="2" t="inlineStr">
         <is>
-          <t>0708.00: Computer Infrastructure and Support (TOP; verify)</t>
+          <t>Computer Infrastructure and Support</t>
         </is>
       </c>
       <c r="F519" s="2" t="inlineStr">
@@ -32636,7 +32636,7 @@
     <row r="520" ht="25.5" customHeight="1">
       <c r="A520" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B520" s="2" t="inlineStr">
@@ -32698,7 +32698,7 @@
     <row r="521" ht="25.5" customHeight="1">
       <c r="A521" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B521" s="2" t="inlineStr">
@@ -32718,7 +32718,7 @@
       </c>
       <c r="E521" s="2" t="inlineStr">
         <is>
-          <t>0602.00: Journalism (TOP; verify)</t>
+          <t>Journalism</t>
         </is>
       </c>
       <c r="F521" s="2" t="inlineStr">
@@ -32760,7 +32760,7 @@
     <row r="522" ht="25.5" customHeight="1">
       <c r="A522" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B522" s="2" t="inlineStr">
@@ -32780,7 +32780,7 @@
       </c>
       <c r="E522" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F522" s="2" t="inlineStr">
@@ -32822,7 +32822,7 @@
     <row r="523" ht="25.5" customHeight="1">
       <c r="A523" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B523" s="2" t="inlineStr">
@@ -32842,7 +32842,7 @@
       </c>
       <c r="E523" s="2" t="inlineStr">
         <is>
-          <t>0604.00: Radio and Television (TOP; verify)</t>
+          <t>Radio and Television</t>
         </is>
       </c>
       <c r="F523" s="2" t="inlineStr">
@@ -32884,7 +32884,7 @@
     <row r="524" ht="25.5" customHeight="1">
       <c r="A524" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B524" s="2" t="inlineStr">
@@ -32904,7 +32904,7 @@
       </c>
       <c r="E524" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F524" s="2" t="inlineStr">
@@ -32946,7 +32946,7 @@
     <row r="525" ht="25.5" customHeight="1">
       <c r="A525" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B525" s="2" t="inlineStr">
@@ -32966,7 +32966,7 @@
       </c>
       <c r="E525" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F525" s="2" t="inlineStr">
@@ -33008,7 +33008,7 @@
     <row r="526" ht="25.5" customHeight="1">
       <c r="A526" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B526" s="2" t="inlineStr">
@@ -33070,7 +33070,7 @@
     <row r="527" ht="25.5" customHeight="1">
       <c r="A527" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B527" s="2" t="inlineStr">
@@ -33132,7 +33132,7 @@
     <row r="528" ht="25.5" customHeight="1">
       <c r="A528" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B528" s="2" t="inlineStr">
@@ -33152,7 +33152,7 @@
       </c>
       <c r="E528" s="2" t="inlineStr">
         <is>
-          <t>0709.00: World Wide Web Administration (TOP; verify)</t>
+          <t>World Wide Web Administration</t>
         </is>
       </c>
       <c r="F528" s="2" t="inlineStr">
@@ -33194,7 +33194,7 @@
     <row r="529" ht="25.5" customHeight="1">
       <c r="A529" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B529" s="2" t="inlineStr">
@@ -33214,7 +33214,7 @@
       </c>
       <c r="E529" s="2" t="inlineStr">
         <is>
-          <t>0610.00: Mass Communications (TOP; verify)</t>
+          <t>Mass Communications</t>
         </is>
       </c>
       <c r="F529" s="2" t="inlineStr">
@@ -33256,7 +33256,7 @@
     <row r="530" ht="25.5" customHeight="1">
       <c r="A530" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B530" s="2" t="inlineStr">
@@ -33276,7 +33276,7 @@
       </c>
       <c r="E530" s="2" t="inlineStr">
         <is>
-          <t>0601.00: Media and Communications, General (TOP; verify)</t>
+          <t>Media and Communications, General</t>
         </is>
       </c>
       <c r="F530" s="2" t="inlineStr">
@@ -33318,7 +33318,7 @@
     <row r="531" ht="25.5" customHeight="1">
       <c r="A531" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B531" s="2" t="inlineStr">
@@ -33338,7 +33338,7 @@
       </c>
       <c r="E531" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F531" s="2" t="inlineStr">
@@ -33380,7 +33380,7 @@
     <row r="532" ht="25.5" customHeight="1">
       <c r="A532" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B532" s="2" t="inlineStr">
@@ -33442,7 +33442,7 @@
     <row r="533" ht="25.5" customHeight="1">
       <c r="A533" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B533" s="2" t="inlineStr">
@@ -33462,7 +33462,7 @@
       </c>
       <c r="E533" s="2" t="inlineStr">
         <is>
-          <t>0709.10: E-Commerce (Technology emphasis) (TOP; verify)</t>
+          <t>E-Commerce (Technology emphasis)</t>
         </is>
       </c>
       <c r="F533" s="2" t="inlineStr">
@@ -33504,7 +33504,7 @@
     <row r="534" ht="25.5" customHeight="1">
       <c r="A534" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B534" s="2" t="inlineStr">
@@ -33524,7 +33524,7 @@
       </c>
       <c r="E534" s="2" t="inlineStr">
         <is>
-          <t>0709.10: E-Commerce (Technology emphasis) (TOP; verify)</t>
+          <t>E-Commerce (Technology emphasis)</t>
         </is>
       </c>
       <c r="F534" s="2" t="inlineStr">
@@ -33566,7 +33566,7 @@
     <row r="535" ht="25.5" customHeight="1">
       <c r="A535" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B535" s="2" t="inlineStr">
@@ -33586,7 +33586,7 @@
       </c>
       <c r="E535" s="2" t="inlineStr">
         <is>
-          <t>0614.00: Digital Media (TOP; verify)</t>
+          <t>Digital Media</t>
         </is>
       </c>
       <c r="F535" s="2" t="inlineStr">
@@ -33628,7 +33628,7 @@
     <row r="536" ht="25.5" customHeight="1">
       <c r="A536" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B536" s="2" t="inlineStr">
@@ -33648,7 +33648,7 @@
       </c>
       <c r="E536" s="2" t="inlineStr">
         <is>
-          <t>0614.00: Digital Media (TOP; verify)</t>
+          <t>Digital Media</t>
         </is>
       </c>
       <c r="F536" s="2" t="inlineStr">
@@ -33690,7 +33690,7 @@
     <row r="537" ht="25.5" customHeight="1">
       <c r="A537" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B537" s="2" t="inlineStr">
@@ -33710,7 +33710,7 @@
       </c>
       <c r="E537" s="2" t="inlineStr">
         <is>
-          <t>0506.40: Small Business and Entrepreneurship (TOP; verify)</t>
+          <t>Small Business and Entrepreneurship</t>
         </is>
       </c>
       <c r="F537" s="2" t="inlineStr">
@@ -33752,7 +33752,7 @@
     <row r="538" ht="25.5" customHeight="1">
       <c r="A538" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B538" s="2" t="inlineStr">
@@ -33814,7 +33814,7 @@
     <row r="539" ht="25.5" customHeight="1">
       <c r="A539" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B539" s="2" t="inlineStr">
@@ -33834,7 +33834,7 @@
       </c>
       <c r="E539" s="2" t="inlineStr">
         <is>
-          <t>0610.00: Mass Communications (TOP; verify)</t>
+          <t>Mass Communications</t>
         </is>
       </c>
       <c r="F539" s="2" t="inlineStr">
@@ -33876,7 +33876,7 @@
     <row r="540" ht="25.5" customHeight="1">
       <c r="A540" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B540" s="2" t="inlineStr">
@@ -33896,7 +33896,7 @@
       </c>
       <c r="E540" s="2" t="inlineStr">
         <is>
-          <t>0610.00: Mass Communications (TOP; verify)</t>
+          <t>Mass Communications</t>
         </is>
       </c>
       <c r="F540" s="2" t="inlineStr">
@@ -33938,7 +33938,7 @@
     <row r="541" ht="25.5" customHeight="1">
       <c r="A541" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B541" s="2" t="inlineStr">
@@ -34000,7 +34000,7 @@
     <row r="542" ht="25.5" customHeight="1">
       <c r="A542" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B542" s="2" t="inlineStr">
@@ -34062,7 +34062,7 @@
     <row r="543" ht="25.5" customHeight="1">
       <c r="A543" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B543" s="2" t="inlineStr">
@@ -34124,7 +34124,7 @@
     <row r="544" ht="25.5" customHeight="1">
       <c r="A544" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B544" s="2" t="inlineStr">
@@ -34186,7 +34186,7 @@
     <row r="545" ht="25.5" customHeight="1">
       <c r="A545" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B545" s="2" t="inlineStr">
@@ -34206,7 +34206,7 @@
       </c>
       <c r="E545" s="2" t="inlineStr">
         <is>
-          <t>0709.10: E-Commerce (Technology emphasis) (TOP; verify)</t>
+          <t>E-Commerce (Technology emphasis)</t>
         </is>
       </c>
       <c r="F545" s="2" t="inlineStr">
@@ -34248,7 +34248,7 @@
     <row r="546" ht="25.5" customHeight="1">
       <c r="A546" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B546" s="2" t="inlineStr">
@@ -34268,7 +34268,7 @@
       </c>
       <c r="E546" s="2" t="inlineStr">
         <is>
-          <t>0602.00: Journalism (TOP; verify)</t>
+          <t>Journalism</t>
         </is>
       </c>
       <c r="F546" s="2" t="inlineStr">
@@ -34310,7 +34310,7 @@
     <row r="547" ht="25.5" customHeight="1">
       <c r="A547" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B547" s="2" t="inlineStr">
@@ -34330,7 +34330,7 @@
       </c>
       <c r="E547" s="2" t="inlineStr">
         <is>
-          <t>0514.00: Office Technology/Office Computer Applications (TOP; verify)</t>
+          <t>Office Technology/Office Computer Applications</t>
         </is>
       </c>
       <c r="F547" s="2" t="inlineStr">
@@ -34372,7 +34372,7 @@
     <row r="548" ht="25.5" customHeight="1">
       <c r="A548" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B548" s="2" t="inlineStr">
@@ -34392,7 +34392,7 @@
       </c>
       <c r="E548" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F548" s="2" t="inlineStr">
@@ -34434,7 +34434,7 @@
     <row r="549" ht="25.5" customHeight="1">
       <c r="A549" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B549" s="2" t="inlineStr">
@@ -34496,7 +34496,7 @@
     <row r="550" ht="25.5" customHeight="1">
       <c r="A550" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B550" s="2" t="inlineStr">
@@ -34558,7 +34558,7 @@
     <row r="551" ht="25.5" customHeight="1">
       <c r="A551" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B551" s="2" t="inlineStr">
@@ -34578,7 +34578,7 @@
       </c>
       <c r="E551" s="2" t="inlineStr">
         <is>
-          <t>0610.00: Mass Communications (TOP; verify)</t>
+          <t>Mass Communications</t>
         </is>
       </c>
       <c r="F551" s="2" t="inlineStr">
@@ -34620,7 +34620,7 @@
     <row r="552" ht="25.5" customHeight="1">
       <c r="A552" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B552" s="2" t="inlineStr">
@@ -34640,7 +34640,7 @@
       </c>
       <c r="E552" s="2" t="inlineStr">
         <is>
-          <t>0601.00: Media and Communications, General (TOP; verify)</t>
+          <t>Media and Communications, General</t>
         </is>
       </c>
       <c r="F552" s="2" t="inlineStr">
@@ -34682,7 +34682,7 @@
     <row r="553" ht="25.5" customHeight="1">
       <c r="A553" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B553" s="2" t="inlineStr">
@@ -34702,7 +34702,7 @@
       </c>
       <c r="E553" s="2" t="inlineStr">
         <is>
-          <t>0799.00: Other Information Technology (TOP; verify)</t>
+          <t>Other Information Technology</t>
         </is>
       </c>
       <c r="F553" s="2" t="inlineStr">
@@ -34744,7 +34744,7 @@
     <row r="554" ht="25.5" customHeight="1">
       <c r="A554" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B554" s="2" t="inlineStr">
@@ -34764,7 +34764,7 @@
       </c>
       <c r="E554" s="2" t="inlineStr">
         <is>
-          <t>0699.00: Other Media and Communications (TOP; verify)</t>
+          <t>Other Media and Communications</t>
         </is>
       </c>
       <c r="F554" s="2" t="inlineStr">
@@ -34806,7 +34806,7 @@
     <row r="555" ht="25.5" customHeight="1">
       <c r="A555" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B555" s="2" t="inlineStr">
@@ -34826,7 +34826,7 @@
       </c>
       <c r="E555" s="2" t="inlineStr">
         <is>
-          <t>0602.00: Journalism (TOP; verify)</t>
+          <t>Journalism</t>
         </is>
       </c>
       <c r="F555" s="2" t="inlineStr">
@@ -34868,7 +34868,7 @@
     <row r="556" ht="25.5" customHeight="1">
       <c r="A556" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B556" s="2" t="inlineStr">
@@ -34888,7 +34888,7 @@
       </c>
       <c r="E556" s="2" t="inlineStr">
         <is>
-          <t>0602.00: Journalism (TOP; verify)</t>
+          <t>Journalism</t>
         </is>
       </c>
       <c r="F556" s="2" t="inlineStr">
@@ -34930,7 +34930,7 @@
     <row r="557" ht="25.5" customHeight="1">
       <c r="A557" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B557" s="2" t="inlineStr">
@@ -34950,7 +34950,7 @@
       </c>
       <c r="E557" s="2" t="inlineStr">
         <is>
-          <t>0509.70: E-Commerce (Business emphasis) (TOP; verify)</t>
+          <t>E-Commerce (Business emphasis)</t>
         </is>
       </c>
       <c r="F557" s="2" t="inlineStr">
@@ -34992,7 +34992,7 @@
     <row r="558" ht="25.5" customHeight="1">
       <c r="A558" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B558" s="2" t="inlineStr">
@@ -35054,7 +35054,7 @@
     <row r="559" ht="25.5" customHeight="1">
       <c r="A559" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B559" s="2" t="inlineStr">
@@ -35116,7 +35116,7 @@
     <row r="560" ht="25.5" customHeight="1">
       <c r="A560" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B560" s="2" t="inlineStr">
@@ -35136,7 +35136,7 @@
       </c>
       <c r="E560" s="2" t="inlineStr">
         <is>
-          <t>0614.00: Digital Media (TOP; verify)</t>
+          <t>Digital Media</t>
         </is>
       </c>
       <c r="F560" s="2" t="inlineStr">
@@ -35178,7 +35178,7 @@
     <row r="561" ht="25.5" customHeight="1">
       <c r="A561" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B561" s="2" t="inlineStr">
@@ -35240,7 +35240,7 @@
     <row r="562" ht="25.5" customHeight="1">
       <c r="A562" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B562" s="2" t="inlineStr">
@@ -35302,7 +35302,7 @@
     <row r="563" ht="25.5" customHeight="1">
       <c r="A563" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B563" s="2" t="inlineStr">
@@ -35364,7 +35364,7 @@
     <row r="564" ht="25.5" customHeight="1">
       <c r="A564" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B564" s="2" t="inlineStr">
@@ -35384,7 +35384,7 @@
       </c>
       <c r="E564" s="2" t="inlineStr">
         <is>
-          <t>0614.30: Website Design and Development (TOP; verify)</t>
+          <t>Website Design and Development</t>
         </is>
       </c>
       <c r="F564" s="2" t="inlineStr">
@@ -35426,7 +35426,7 @@
     <row r="565" ht="25.5" customHeight="1">
       <c r="A565" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B565" s="2" t="inlineStr">
@@ -35446,7 +35446,7 @@
       </c>
       <c r="E565" s="2" t="inlineStr">
         <is>
-          <t>0614.30: Website Design and Development (TOP; verify)</t>
+          <t>Website Design and Development</t>
         </is>
       </c>
       <c r="F565" s="2" t="inlineStr">
@@ -35488,7 +35488,7 @@
     <row r="566" ht="25.5" customHeight="1">
       <c r="A566" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B566" s="2" t="inlineStr">
@@ -35508,7 +35508,7 @@
       </c>
       <c r="E566" s="2" t="inlineStr">
         <is>
-          <t>0614.30: Website Design and Development (TOP; verify)</t>
+          <t>Website Design and Development</t>
         </is>
       </c>
       <c r="F566" s="2" t="inlineStr">
@@ -35550,7 +35550,7 @@
     <row r="567" ht="25.5" customHeight="1">
       <c r="A567" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B567" s="2" t="inlineStr">
@@ -35570,7 +35570,7 @@
       </c>
       <c r="E567" s="2" t="inlineStr">
         <is>
-          <t>1012.00: Applied Photography (TOP; verify)</t>
+          <t>Applied Photography</t>
         </is>
       </c>
       <c r="F567" s="2" t="inlineStr">
@@ -35612,7 +35612,7 @@
     <row r="568" ht="25.5" customHeight="1">
       <c r="A568" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B568" s="2" t="inlineStr">
@@ -35632,7 +35632,7 @@
       </c>
       <c r="E568" s="2" t="inlineStr">
         <is>
-          <t>0604.00: Radio and Television (TOP; verify)</t>
+          <t>Radio and Television</t>
         </is>
       </c>
       <c r="F568" s="2" t="inlineStr">
@@ -35674,7 +35674,7 @@
     <row r="569" ht="25.5" customHeight="1">
       <c r="A569" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B569" s="2" t="inlineStr">
@@ -35736,7 +35736,7 @@
     <row r="570" ht="25.5" customHeight="1">
       <c r="A570" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B570" s="2" t="inlineStr">
@@ -35756,7 +35756,7 @@
       </c>
       <c r="E570" s="2" t="inlineStr">
         <is>
-          <t>1030.00: Graphic Art and Design (TOP; verify)</t>
+          <t>Graphic Art and Design</t>
         </is>
       </c>
       <c r="F570" s="2" t="inlineStr">
@@ -35798,7 +35798,7 @@
     <row r="571" ht="25.5" customHeight="1">
       <c r="A571" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B571" s="2" t="inlineStr">
@@ -35818,7 +35818,7 @@
       </c>
       <c r="E571" s="2" t="inlineStr">
         <is>
-          <t>0604.00: Radio and Television (TOP; verify)</t>
+          <t>Radio and Television</t>
         </is>
       </c>
       <c r="F571" s="2" t="inlineStr">
@@ -35860,7 +35860,7 @@
     <row r="572" ht="25.5" customHeight="1">
       <c r="A572" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B572" s="2" t="inlineStr">
@@ -35922,7 +35922,7 @@
     <row r="573" ht="25.5" customHeight="1">
       <c r="A573" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B573" s="2" t="inlineStr">
@@ -35942,7 +35942,7 @@
       </c>
       <c r="E573" s="2" t="inlineStr">
         <is>
-          <t>1030.00: Graphic Art and Design (TOP; verify)</t>
+          <t>Graphic Art and Design</t>
         </is>
       </c>
       <c r="F573" s="2" t="inlineStr">
@@ -35984,7 +35984,7 @@
     <row r="574" ht="25.5" customHeight="1">
       <c r="A574" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B574" s="2" t="inlineStr">
@@ -36004,7 +36004,7 @@
       </c>
       <c r="E574" s="2" t="inlineStr">
         <is>
-          <t>0506.40: Small Business and Entrepreneurship (TOP; verify)</t>
+          <t>Small Business and Entrepreneurship</t>
         </is>
       </c>
       <c r="F574" s="2" t="inlineStr">
@@ -36046,7 +36046,7 @@
     <row r="575" ht="25.5" customHeight="1">
       <c r="A575" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B575" s="2" t="inlineStr">
@@ -36066,7 +36066,7 @@
       </c>
       <c r="E575" s="2" t="inlineStr">
         <is>
-          <t>0506.40: Small Business and Entrepreneurship (TOP; verify)</t>
+          <t>Small Business and Entrepreneurship</t>
         </is>
       </c>
       <c r="F575" s="2" t="inlineStr">
@@ -36108,7 +36108,7 @@
     <row r="576" ht="25.5" customHeight="1">
       <c r="A576" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B576" s="2" t="inlineStr">
@@ -36170,7 +36170,7 @@
     <row r="577" ht="25.5" customHeight="1">
       <c r="A577" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B577" s="2" t="inlineStr">
@@ -36190,7 +36190,7 @@
       </c>
       <c r="E577" s="2" t="inlineStr">
         <is>
-          <t>0602.00: Journalism (TOP; verify)</t>
+          <t>Journalism</t>
         </is>
       </c>
       <c r="F577" s="2" t="inlineStr">
@@ -36232,7 +36232,7 @@
     <row r="578" ht="25.5" customHeight="1">
       <c r="A578" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B578" s="2" t="inlineStr">
@@ -36252,7 +36252,7 @@
       </c>
       <c r="E578" s="2" t="inlineStr">
         <is>
-          <t>0606.00: Public Relations (TOP; verify)</t>
+          <t>Public Relations</t>
         </is>
       </c>
       <c r="F578" s="2" t="inlineStr">
@@ -36294,7 +36294,7 @@
     <row r="579" ht="25.5" customHeight="1">
       <c r="A579" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B579" s="2" t="inlineStr">
@@ -36356,7 +36356,7 @@
     <row r="580" ht="25.5" customHeight="1">
       <c r="A580" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B580" s="2" t="inlineStr">
@@ -36376,7 +36376,7 @@
       </c>
       <c r="E580" s="2" t="inlineStr">
         <is>
-          <t>1030.00: Graphic Art and Design (TOP; verify)</t>
+          <t>Graphic Art and Design</t>
         </is>
       </c>
       <c r="F580" s="2" t="inlineStr">
@@ -36418,7 +36418,7 @@
     <row r="581" ht="25.5" customHeight="1">
       <c r="A581" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B581" s="2" t="inlineStr">
@@ -36480,7 +36480,7 @@
     <row r="582" ht="25.5" customHeight="1">
       <c r="A582" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B582" s="2" t="inlineStr">
@@ -36542,7 +36542,7 @@
     <row r="583" ht="25.5" customHeight="1">
       <c r="A583" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B583" s="2" t="inlineStr">
@@ -36562,7 +36562,7 @@
       </c>
       <c r="E583" s="2" t="inlineStr">
         <is>
-          <t>0614.00: Digital Media (TOP; verify)</t>
+          <t>Digital Media</t>
         </is>
       </c>
       <c r="F583" s="2" t="inlineStr">
@@ -36604,7 +36604,7 @@
     <row r="584" ht="25.5" customHeight="1">
       <c r="A584" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B584" s="2" t="inlineStr">
@@ -36666,7 +36666,7 @@
     <row r="585" ht="25.5" customHeight="1">
       <c r="A585" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B585" s="2" t="inlineStr">
@@ -36686,7 +36686,7 @@
       </c>
       <c r="E585" s="2" t="inlineStr">
         <is>
-          <t>0506.00: Business Management (TOP; verify)</t>
+          <t>Business Management</t>
         </is>
       </c>
       <c r="F585" s="2" t="inlineStr">
@@ -36728,7 +36728,7 @@
     <row r="586" ht="25.5" customHeight="1">
       <c r="A586" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B586" s="2" t="inlineStr">
@@ -36748,7 +36748,7 @@
       </c>
       <c r="E586" s="2" t="inlineStr">
         <is>
-          <t>0602.00: Journalism (TOP; verify)</t>
+          <t>Journalism</t>
         </is>
       </c>
       <c r="F586" s="2" t="inlineStr">
@@ -36790,7 +36790,7 @@
     <row r="587" ht="25.5" customHeight="1">
       <c r="A587" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B587" s="2" t="inlineStr">
@@ -36852,7 +36852,7 @@
     <row r="588" ht="25.5" customHeight="1">
       <c r="A588" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B588" s="2" t="inlineStr">
@@ -36914,7 +36914,7 @@
     <row r="589" ht="25.5" customHeight="1">
       <c r="A589" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B589" s="2" t="inlineStr">
@@ -36934,7 +36934,7 @@
       </c>
       <c r="E589" s="2" t="inlineStr">
         <is>
-          <t>0606.00: Public Relations (TOP; verify)</t>
+          <t>Public Relations</t>
         </is>
       </c>
       <c r="F589" s="2" t="inlineStr">
@@ -36976,7 +36976,7 @@
     <row r="590" ht="25.5" customHeight="1">
       <c r="A590" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B590" s="2" t="inlineStr">
@@ -36996,7 +36996,7 @@
       </c>
       <c r="E590" s="2" t="inlineStr">
         <is>
-          <t>0606.00: Public Relations (TOP; verify)</t>
+          <t>Public Relations</t>
         </is>
       </c>
       <c r="F590" s="2" t="inlineStr">
@@ -37038,7 +37038,7 @@
     <row r="591" ht="25.5" customHeight="1">
       <c r="A591" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B591" s="2" t="inlineStr">
@@ -37058,7 +37058,7 @@
       </c>
       <c r="E591" s="2" t="inlineStr">
         <is>
-          <t>0606.00: Public Relations (TOP; verify)</t>
+          <t>Public Relations</t>
         </is>
       </c>
       <c r="F591" s="2" t="inlineStr">
@@ -37100,7 +37100,7 @@
     <row r="592" ht="25.5" customHeight="1">
       <c r="A592" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B592" s="2" t="inlineStr">
@@ -37162,7 +37162,7 @@
     <row r="593" ht="25.5" customHeight="1">
       <c r="A593" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B593" s="2" t="inlineStr">
@@ -37224,7 +37224,7 @@
     <row r="594" ht="25.5" customHeight="1">
       <c r="A594" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B594" s="2" t="inlineStr">
@@ -37244,7 +37244,7 @@
       </c>
       <c r="E594" s="2" t="inlineStr">
         <is>
-          <t>1030.00: Graphic Art and Design (TOP; verify)</t>
+          <t>Graphic Art and Design</t>
         </is>
       </c>
       <c r="F594" s="2" t="inlineStr">
@@ -37286,7 +37286,7 @@
     <row r="595" ht="25.5" customHeight="1">
       <c r="A595" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B595" s="2" t="inlineStr">
@@ -37348,7 +37348,7 @@
     <row r="596" ht="25.5" customHeight="1">
       <c r="A596" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B596" s="2" t="inlineStr">
@@ -37368,7 +37368,7 @@
       </c>
       <c r="E596" s="2" t="inlineStr">
         <is>
-          <t>0599.00: Other Business and Management (TOP; verify)</t>
+          <t>Other Business and Management</t>
         </is>
       </c>
       <c r="F596" s="2" t="inlineStr">
@@ -37410,7 +37410,7 @@
     <row r="597" ht="25.5" customHeight="1">
       <c r="A597" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B597" s="2" t="inlineStr">
@@ -37430,7 +37430,7 @@
       </c>
       <c r="E597" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F597" s="2" t="inlineStr">
@@ -37472,7 +37472,7 @@
     <row r="598" ht="25.5" customHeight="1">
       <c r="A598" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B598" s="2" t="inlineStr">
@@ -37492,7 +37492,7 @@
       </c>
       <c r="E598" s="2" t="inlineStr">
         <is>
-          <t>0509.00: Marketing and Distribution (TOP; verify)</t>
+          <t>Marketing and Distribution</t>
         </is>
       </c>
       <c r="F598" s="2" t="inlineStr">
@@ -37534,7 +37534,7 @@
     <row r="599" ht="25.5" customHeight="1">
       <c r="A599" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B599" s="2" t="inlineStr">
@@ -37596,7 +37596,7 @@
     <row r="600" ht="25.5" customHeight="1">
       <c r="A600" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B600" s="2" t="inlineStr">
@@ -37616,7 +37616,7 @@
       </c>
       <c r="E600" s="2" t="inlineStr">
         <is>
-          <t>0514.00: Office Technology/Office Computer Applications (TOP; verify)</t>
+          <t>Office Technology/Office Computer Applications</t>
         </is>
       </c>
       <c r="F600" s="2" t="inlineStr">
@@ -37658,7 +37658,7 @@
     <row r="601" ht="25.5" customHeight="1">
       <c r="A601" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B601" s="2" t="inlineStr">
@@ -37720,7 +37720,7 @@
     <row r="602" ht="25.5" customHeight="1">
       <c r="A602" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B602" s="2" t="inlineStr">
@@ -37782,7 +37782,7 @@
     <row r="603" ht="25.5" customHeight="1">
       <c r="A603" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B603" s="2" t="inlineStr">
@@ -37802,7 +37802,7 @@
       </c>
       <c r="E603" s="2" t="inlineStr">
         <is>
-          <t>0510.00: Logistics and Materials Transportation (TOP; verify)</t>
+          <t>Logistics and Materials Transportation</t>
         </is>
       </c>
       <c r="F603" s="2" t="inlineStr">
@@ -37844,7 +37844,7 @@
     <row r="604" ht="25.5" customHeight="1">
       <c r="A604" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B604" s="2" t="inlineStr">
@@ -37906,7 +37906,7 @@
     <row r="605" ht="25.5" customHeight="1">
       <c r="A605" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B605" s="2" t="inlineStr">
@@ -37968,7 +37968,7 @@
     <row r="606" ht="25.5" customHeight="1">
       <c r="A606" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B606" s="2" t="inlineStr">
@@ -38030,7 +38030,7 @@
     <row r="607" ht="25.5" customHeight="1">
       <c r="A607" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B607" s="2" t="inlineStr">
@@ -38092,7 +38092,7 @@
     <row r="608" ht="25.5" customHeight="1">
       <c r="A608" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B608" s="2" t="inlineStr">
@@ -38154,7 +38154,7 @@
     <row r="609" ht="25.5" customHeight="1">
       <c r="A609" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B609" s="2" t="inlineStr">
@@ -38216,7 +38216,7 @@
     <row r="610" ht="25.5" customHeight="1">
       <c r="A610" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B610" s="2" t="inlineStr">
@@ -38278,7 +38278,7 @@
     <row r="611" ht="25.5" customHeight="1">
       <c r="A611" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B611" s="2" t="inlineStr">
@@ -38340,7 +38340,7 @@
     <row r="612" ht="25.5" customHeight="1">
       <c r="A612" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B612" s="2" t="inlineStr">
@@ -38402,7 +38402,7 @@
     <row r="613" ht="25.5" customHeight="1">
       <c r="A613" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B613" s="2" t="inlineStr">
@@ -38422,7 +38422,7 @@
       </c>
       <c r="E613" s="2" t="inlineStr">
         <is>
-          <t>0702.00: Computer Information Systems (TOP; verify)</t>
+          <t>Computer Information Systems</t>
         </is>
       </c>
       <c r="F613" s="2" t="inlineStr">
@@ -38464,7 +38464,7 @@
     <row r="614" ht="25.5" customHeight="1">
       <c r="A614" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B614" s="2" t="inlineStr">
@@ -38526,7 +38526,7 @@
     <row r="615" ht="25.5" customHeight="1">
       <c r="A615" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B615" s="2" t="inlineStr">
@@ -38588,7 +38588,7 @@
     <row r="616" ht="25.5" customHeight="1">
       <c r="A616" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B616" s="2" t="inlineStr">
@@ -38650,7 +38650,7 @@
     <row r="617" ht="25.5" customHeight="1">
       <c r="A617" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B617" s="2" t="inlineStr">
@@ -38670,7 +38670,7 @@
       </c>
       <c r="E617" s="2" t="inlineStr">
         <is>
-          <t>1307.00: Hospitality (TOP; verify)</t>
+          <t>Hospitality</t>
         </is>
       </c>
       <c r="F617" s="2" t="inlineStr">
@@ -38712,7 +38712,7 @@
     <row r="618" ht="25.5" customHeight="1">
       <c r="A618" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B618" s="2" t="inlineStr">
@@ -38732,7 +38732,7 @@
       </c>
       <c r="E618" s="2" t="inlineStr">
         <is>
-          <t>0614.30: Website Design and Development (TOP; verify)</t>
+          <t>Website Design and Development</t>
         </is>
       </c>
       <c r="F618" s="2" t="inlineStr">
@@ -38774,7 +38774,7 @@
     <row r="619" ht="25.5" customHeight="1">
       <c r="A619" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B619" s="2" t="inlineStr">
@@ -38794,7 +38794,7 @@
       </c>
       <c r="E619" s="2" t="inlineStr">
         <is>
-          <t>0514.00: Office Technology/Office Computer Applications (TOP; verify)</t>
+          <t>Office Technology/Office Computer Applications</t>
         </is>
       </c>
       <c r="F619" s="2" t="inlineStr">
@@ -38836,7 +38836,7 @@
     <row r="620" ht="25.5" customHeight="1">
       <c r="A620" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B620" s="2" t="inlineStr">
@@ -38898,7 +38898,7 @@
     <row r="621" ht="25.5" customHeight="1">
       <c r="A621" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B621" s="2" t="inlineStr">
@@ -38960,7 +38960,7 @@
     <row r="622" ht="25.5" customHeight="1">
       <c r="A622" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B622" s="2" t="inlineStr">
@@ -38980,7 +38980,7 @@
       </c>
       <c r="E622" s="2" t="inlineStr">
         <is>
-          <t>0709.00: World Wide Web Administration (TOP; verify)</t>
+          <t>World Wide Web Administration</t>
         </is>
       </c>
       <c r="F622" s="2" t="inlineStr">
@@ -39022,7 +39022,7 @@
     <row r="623" ht="25.5" customHeight="1">
       <c r="A623" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B623" s="2" t="inlineStr">
@@ -39042,7 +39042,7 @@
       </c>
       <c r="E623" s="2" t="inlineStr">
         <is>
-          <t>0614.00: Digital Media (TOP; verify)</t>
+          <t>Digital Media</t>
         </is>
       </c>
       <c r="F623" s="2" t="inlineStr">
@@ -39084,7 +39084,7 @@
     <row r="624" ht="25.5" customHeight="1">
       <c r="A624" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B624" s="2" t="inlineStr">
@@ -39104,7 +39104,7 @@
       </c>
       <c r="E624" s="2" t="inlineStr">
         <is>
-          <t>0614.00: Digital Media (TOP; verify)</t>
+          <t>Digital Media</t>
         </is>
       </c>
       <c r="F624" s="2" t="inlineStr">
@@ -39146,7 +39146,7 @@
     <row r="625" ht="25.5" customHeight="1">
       <c r="A625" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B625" s="2" t="inlineStr">
@@ -39166,7 +39166,7 @@
       </c>
       <c r="E625" s="2" t="inlineStr">
         <is>
-          <t>0604.00: Radio and Television (TOP; verify)</t>
+          <t>Radio and Television</t>
         </is>
       </c>
       <c r="F625" s="2" t="inlineStr">
@@ -39208,7 +39208,7 @@
     <row r="626" ht="25.5" customHeight="1">
       <c r="A626" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B626" s="2" t="inlineStr">
@@ -39228,7 +39228,7 @@
       </c>
       <c r="E626" s="2" t="inlineStr">
         <is>
-          <t>0602.00: Journalism (TOP; verify)</t>
+          <t>Journalism</t>
         </is>
       </c>
       <c r="F626" s="2" t="inlineStr">
@@ -39270,7 +39270,7 @@
     <row r="627" ht="25.5" customHeight="1">
       <c r="A627" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B627" s="2" t="inlineStr">
@@ -39290,7 +39290,7 @@
       </c>
       <c r="E627" s="2" t="inlineStr">
         <is>
-          <t>0511.00: Real Estate (TOP; verify)</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F627" s="2" t="inlineStr">
@@ -39332,7 +39332,7 @@
     <row r="628" ht="25.5" customHeight="1">
       <c r="A628" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B628" s="2" t="inlineStr">
@@ -39394,7 +39394,7 @@
     <row r="629" ht="25.5" customHeight="1">
       <c r="A629" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B629" s="2" t="inlineStr">
@@ -39456,7 +39456,7 @@
     <row r="630" ht="25.5" customHeight="1">
       <c r="A630" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B630" s="2" t="inlineStr">
@@ -39518,7 +39518,7 @@
     <row r="631" ht="25.5" customHeight="1">
       <c r="A631" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B631" s="2" t="inlineStr">
@@ -39580,7 +39580,7 @@
     <row r="632" ht="25.5" customHeight="1">
       <c r="A632" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B632" s="2" t="inlineStr">
@@ -39600,7 +39600,7 @@
       </c>
       <c r="E632" s="2" t="inlineStr">
         <is>
-          <t>0701.00: Information Technology, General (TOP; verify)</t>
+          <t>Information Technology, General</t>
         </is>
       </c>
       <c r="F632" s="2" t="inlineStr">
@@ -39642,7 +39642,7 @@
     <row r="633" ht="25.5" customHeight="1">
       <c r="A633" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B633" s="2" t="inlineStr">
@@ -39704,7 +39704,7 @@
     <row r="634" ht="25.5" customHeight="1">
       <c r="A634" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B634" s="2" t="inlineStr">
@@ -39724,7 +39724,7 @@
       </c>
       <c r="E634" s="2" t="inlineStr">
         <is>
-          <t>0614.30: Website Design and Development (TOP; verify)</t>
+          <t>Website Design and Development</t>
         </is>
       </c>
       <c r="F634" s="2" t="inlineStr">
@@ -39766,7 +39766,7 @@
     <row r="635" ht="25.5" customHeight="1">
       <c r="A635" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B635" s="2" t="inlineStr">
@@ -39786,7 +39786,7 @@
       </c>
       <c r="E635" s="2" t="inlineStr">
         <is>
-          <t>0614.30: Website Design and Development (TOP; verify)</t>
+          <t>Website Design and Development</t>
         </is>
       </c>
       <c r="F635" s="2" t="inlineStr">
@@ -39828,7 +39828,7 @@
     <row r="636" ht="25.5" customHeight="1">
       <c r="A636" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B636" s="2" t="inlineStr">
@@ -39890,7 +39890,7 @@
     <row r="637" ht="25.5" customHeight="1">
       <c r="A637" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B637" s="2" t="inlineStr">
@@ -39952,7 +39952,7 @@
     <row r="638" ht="25.5" customHeight="1">
       <c r="A638" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B638" s="2" t="inlineStr">
@@ -39972,7 +39972,7 @@
       </c>
       <c r="E638" s="2" t="inlineStr">
         <is>
-          <t>1030.00: Graphic Art and Design (TOP; verify)</t>
+          <t>Graphic Art and Design</t>
         </is>
       </c>
       <c r="F638" s="2" t="inlineStr">
@@ -40014,7 +40014,7 @@
     <row r="639" ht="25.5" customHeight="1">
       <c r="A639" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B639" s="2" t="inlineStr">
@@ -40034,7 +40034,7 @@
       </c>
       <c r="E639" s="2" t="inlineStr">
         <is>
-          <t>0614.00: Digital Media (TOP; verify)</t>
+          <t>Digital Media</t>
         </is>
       </c>
       <c r="F639" s="2" t="inlineStr">
@@ -40076,7 +40076,7 @@
     <row r="640" ht="25.5" customHeight="1">
       <c r="A640" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B640" s="2" t="inlineStr">
@@ -40096,7 +40096,7 @@
       </c>
       <c r="E640" s="2" t="inlineStr">
         <is>
-          <t>1030.00: Graphic Art and Design (TOP; verify)</t>
+          <t>Graphic Art and Design</t>
         </is>
       </c>
       <c r="F640" s="2" t="inlineStr">
@@ -40138,7 +40138,7 @@
     <row r="641" ht="25.5" customHeight="1">
       <c r="A641" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B641" s="2" t="inlineStr">
@@ -40158,7 +40158,7 @@
       </c>
       <c r="E641" s="2" t="inlineStr">
         <is>
-          <t>1030.00: Graphic Art and Design (TOP; verify)</t>
+          <t>Graphic Art and Design</t>
         </is>
       </c>
       <c r="F641" s="2" t="inlineStr">
@@ -40200,7 +40200,7 @@
     <row r="642" ht="25.5" customHeight="1">
       <c r="A642" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B642" s="2" t="inlineStr">
@@ -40262,7 +40262,7 @@
     <row r="643" ht="25.5" customHeight="1">
       <c r="A643" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B643" s="2" t="inlineStr">
@@ -40324,7 +40324,7 @@
     <row r="644" ht="25.5" customHeight="1">
       <c r="A644" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B644" s="2" t="inlineStr">
@@ -40386,7 +40386,7 @@
     <row r="645" ht="25.5" customHeight="1">
       <c r="A645" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B645" s="2" t="inlineStr">
@@ -40448,7 +40448,7 @@
     <row r="646" ht="25.5" customHeight="1">
       <c r="A646" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B646" s="2" t="inlineStr">
@@ -40468,7 +40468,7 @@
       </c>
       <c r="E646" s="2" t="inlineStr">
         <is>
-          <t>1030.00: Graphic Art and Design (TOP; verify)</t>
+          <t>Graphic Art and Design</t>
         </is>
       </c>
       <c r="F646" s="2" t="inlineStr">
@@ -40510,7 +40510,7 @@
     <row r="647" ht="25.5" customHeight="1">
       <c r="A647" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B647" s="2" t="inlineStr">
@@ -40530,7 +40530,7 @@
       </c>
       <c r="E647" s="2" t="inlineStr">
         <is>
-          <t>0614.30: Website Design and Development (TOP; verify)</t>
+          <t>Website Design and Development</t>
         </is>
       </c>
       <c r="F647" s="2" t="inlineStr">
@@ -40572,7 +40572,7 @@
     <row r="648" ht="25.5" customHeight="1">
       <c r="A648" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B648" s="2" t="inlineStr">
@@ -40592,7 +40592,7 @@
       </c>
       <c r="E648" s="2" t="inlineStr">
         <is>
-          <t>0614.30: Website Design and Development (TOP; verify)</t>
+          <t>Website Design and Development</t>
         </is>
       </c>
       <c r="F648" s="2" t="inlineStr">
@@ -40634,7 +40634,7 @@
     <row r="649" ht="25.5" customHeight="1">
       <c r="A649" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B649" s="2" t="inlineStr">
@@ -40654,7 +40654,7 @@
       </c>
       <c r="E649" s="2" t="inlineStr">
         <is>
-          <t>0701.00: Information Technology, General (TOP; verify)</t>
+          <t>Information Technology, General</t>
         </is>
       </c>
       <c r="F649" s="2" t="inlineStr">
@@ -40696,7 +40696,7 @@
     <row r="650" ht="25.5" customHeight="1">
       <c r="A650" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B650" s="2" t="inlineStr">
@@ -40716,7 +40716,7 @@
       </c>
       <c r="E650" s="2" t="inlineStr">
         <is>
-          <t>0701.00: Information Technology, General (TOP; verify)</t>
+          <t>Information Technology, General</t>
         </is>
       </c>
       <c r="F650" s="2" t="inlineStr">
@@ -40758,7 +40758,7 @@
     <row r="651" ht="25.5" customHeight="1">
       <c r="A651" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B651" s="2" t="inlineStr">
@@ -40778,7 +40778,7 @@
       </c>
       <c r="E651" s="2" t="inlineStr">
         <is>
-          <t>0614.30: Website Design and Development (TOP; verify)</t>
+          <t>Website Design and Development</t>
         </is>
       </c>
       <c r="F651" s="2" t="inlineStr">
@@ -40820,7 +40820,7 @@
     <row r="652" ht="25.5" customHeight="1">
       <c r="A652" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B652" s="2" t="inlineStr">
@@ -40840,7 +40840,7 @@
       </c>
       <c r="E652" s="2" t="inlineStr">
         <is>
-          <t>0614.30: Website Design and Development (TOP; verify)</t>
+          <t>Website Design and Development</t>
         </is>
       </c>
       <c r="F652" s="2" t="inlineStr">
@@ -40882,7 +40882,7 @@
     <row r="653" ht="25.5" customHeight="1">
       <c r="A653" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B653" s="2" t="inlineStr">
@@ -40902,7 +40902,7 @@
       </c>
       <c r="E653" s="2" t="inlineStr">
         <is>
-          <t>1030.00: Graphic Art and Design (TOP; verify)</t>
+          <t>Graphic Art and Design</t>
         </is>
       </c>
       <c r="F653" s="2" t="inlineStr">
@@ -40944,7 +40944,7 @@
     <row r="654" ht="25.5" customHeight="1">
       <c r="A654" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B654" s="2" t="inlineStr">
@@ -41006,7 +41006,7 @@
     <row r="655" ht="25.5" customHeight="1">
       <c r="A655" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B655" s="2" t="inlineStr">
@@ -41026,7 +41026,7 @@
       </c>
       <c r="E655" s="2" t="inlineStr">
         <is>
-          <t>1030.00: Graphic Art and Design (TOP; verify)</t>
+          <t>Graphic Art and Design</t>
         </is>
       </c>
       <c r="F655" s="2" t="inlineStr">
@@ -41068,7 +41068,7 @@
     <row r="656" ht="25.5" customHeight="1">
       <c r="A656" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B656" s="2" t="inlineStr">
@@ -41088,7 +41088,7 @@
       </c>
       <c r="E656" s="2" t="inlineStr">
         <is>
-          <t>0614.10: Multimedia (TOP; verify)</t>
+          <t>Multimedia</t>
         </is>
       </c>
       <c r="F656" s="2" t="inlineStr">
@@ -41130,7 +41130,7 @@
     <row r="657" ht="25.5" customHeight="1">
       <c r="A657" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B657" s="2" t="inlineStr">
@@ -41150,7 +41150,7 @@
       </c>
       <c r="E657" s="2" t="inlineStr">
         <is>
-          <t>1030.00: Graphic Art and Design (TOP; verify)</t>
+          <t>Graphic Art and Design</t>
         </is>
       </c>
       <c r="F657" s="2" t="inlineStr">
@@ -41192,7 +41192,7 @@
     <row r="658" ht="25.5" customHeight="1">
       <c r="A658" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B658" s="2" t="inlineStr">
@@ -41212,7 +41212,7 @@
       </c>
       <c r="E658" s="2" t="inlineStr">
         <is>
-          <t>1030.00: Graphic Art and Design (TOP; verify)</t>
+          <t>Graphic Art and Design</t>
         </is>
       </c>
       <c r="F658" s="2" t="inlineStr">
@@ -41254,7 +41254,7 @@
     <row r="659" ht="25.5" customHeight="1">
       <c r="A659" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B659" s="2" t="inlineStr">
@@ -41274,7 +41274,7 @@
       </c>
       <c r="E659" s="2" t="inlineStr">
         <is>
-          <t>1030.00: Graphic Art and Design (TOP; verify)</t>
+          <t>Graphic Art and Design</t>
         </is>
       </c>
       <c r="F659" s="2" t="inlineStr">
@@ -41316,7 +41316,7 @@
     <row r="660" ht="25.5" customHeight="1">
       <c r="A660" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B660" s="2" t="inlineStr">
@@ -41336,7 +41336,7 @@
       </c>
       <c r="E660" s="2" t="inlineStr">
         <is>
-          <t>1099.00: Other Fine and Applied Arts (TOP; verify)</t>
+          <t>Other Fine and Applied Arts</t>
         </is>
       </c>
       <c r="F660" s="2" t="inlineStr">
@@ -41378,7 +41378,7 @@
     <row r="661" ht="25.5" customHeight="1">
       <c r="A661" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B661" s="2" t="inlineStr">
@@ -41440,7 +41440,7 @@
     <row r="662" ht="25.5" customHeight="1">
       <c r="A662" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B662" s="2" t="inlineStr">
@@ -41460,7 +41460,7 @@
       </c>
       <c r="E662" s="2" t="inlineStr">
         <is>
-          <t>1030.00: Graphic Art and Design (TOP; verify)</t>
+          <t>Graphic Art and Design</t>
         </is>
       </c>
       <c r="F662" s="2" t="inlineStr">
@@ -41502,7 +41502,7 @@
     <row r="663" ht="25.5" customHeight="1">
       <c r="A663" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B663" s="2" t="inlineStr">
@@ -41522,7 +41522,7 @@
       </c>
       <c r="E663" s="2" t="inlineStr">
         <is>
-          <t>0614.00: Digital Media (TOP; verify)</t>
+          <t>Digital Media</t>
         </is>
       </c>
       <c r="F663" s="2" t="inlineStr">
@@ -41564,7 +41564,7 @@
     <row r="664" ht="25.5" customHeight="1">
       <c r="A664" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B664" s="2" t="inlineStr">
@@ -41584,7 +41584,7 @@
       </c>
       <c r="E664" s="2" t="inlineStr">
         <is>
-          <t>1030.00: Graphic Art and Design (TOP; verify)</t>
+          <t>Graphic Art and Design</t>
         </is>
       </c>
       <c r="F664" s="2" t="inlineStr">
@@ -41626,7 +41626,7 @@
     <row r="665" ht="25.5" customHeight="1">
       <c r="A665" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B665" s="2" t="inlineStr">
@@ -41646,7 +41646,7 @@
       </c>
       <c r="E665" s="2" t="inlineStr">
         <is>
-          <t>1030.00: Graphic Art and Design (TOP; verify)</t>
+          <t>Graphic Art and Design</t>
         </is>
       </c>
       <c r="F665" s="2" t="inlineStr">
@@ -41688,7 +41688,7 @@
     <row r="666" ht="25.5" customHeight="1">
       <c r="A666" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B666" s="2" t="inlineStr">
@@ -41708,7 +41708,7 @@
       </c>
       <c r="E666" s="2" t="inlineStr">
         <is>
-          <t>1030.00: Graphic Art and Design (TOP; verify)</t>
+          <t>Graphic Art and Design</t>
         </is>
       </c>
       <c r="F666" s="2" t="inlineStr">
@@ -41750,7 +41750,7 @@
     <row r="667" ht="25.5" customHeight="1">
       <c r="A667" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B667" s="2" t="inlineStr">
@@ -41770,7 +41770,7 @@
       </c>
       <c r="E667" s="2" t="inlineStr">
         <is>
-          <t>1030.00: Graphic Art and Design (TOP; verify)</t>
+          <t>Graphic Art and Design</t>
         </is>
       </c>
       <c r="F667" s="2" t="inlineStr">
@@ -41812,7 +41812,7 @@
     <row r="668" ht="25.5" customHeight="1">
       <c r="A668" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B668" s="2" t="inlineStr">
@@ -41832,7 +41832,7 @@
       </c>
       <c r="E668" s="2" t="inlineStr">
         <is>
-          <t>1030.00: Graphic Art and Design (TOP; verify)</t>
+          <t>Graphic Art and Design</t>
         </is>
       </c>
       <c r="F668" s="2" t="inlineStr">
@@ -41874,7 +41874,7 @@
     <row r="669" ht="25.5" customHeight="1">
       <c r="A669" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B669" s="2" t="inlineStr">
@@ -41894,7 +41894,7 @@
       </c>
       <c r="E669" s="2" t="inlineStr">
         <is>
-          <t>1030.00: Graphic Art and Design (TOP; verify)</t>
+          <t>Graphic Art and Design</t>
         </is>
       </c>
       <c r="F669" s="2" t="inlineStr">
@@ -41936,7 +41936,7 @@
     <row r="670" ht="25.5" customHeight="1">
       <c r="A670" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B670" s="2" t="inlineStr">
@@ -41956,7 +41956,7 @@
       </c>
       <c r="E670" s="2" t="inlineStr">
         <is>
-          <t>1030.00: Graphic Art and Design (TOP; verify)</t>
+          <t>Graphic Art and Design</t>
         </is>
       </c>
       <c r="F670" s="2" t="inlineStr">
@@ -41998,7 +41998,7 @@
     <row r="671" ht="25.5" customHeight="1">
       <c r="A671" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B671" s="2" t="inlineStr">
@@ -42060,7 +42060,7 @@
     <row r="672" ht="25.5" customHeight="1">
       <c r="A672" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B672" s="2" t="inlineStr">
@@ -42122,7 +42122,7 @@
     <row r="673" ht="25.5" customHeight="1">
       <c r="A673" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B673" s="2" t="inlineStr">
@@ -42184,7 +42184,7 @@
     <row r="674" ht="25.5" customHeight="1">
       <c r="A674" s="2" t="inlineStr">
         <is>
-          <t>Digital Marketer (O*NET 13-1161.01 Search Marketing Strategists)</t>
+          <t>Digital Marketer</t>
         </is>
       </c>
       <c r="B674" s="2" t="inlineStr">
@@ -42299,7 +42299,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Region is the Strong Workforce Program region. Discipline is the Minimum Qualifications discipline where the subject code maps without ambiguity; otherwise the TOP code, marked 'verify'.</t>
+          <t>Region is the Strong Workforce Program region. Discipline is the Minimum Qualifications discipline where the subject code maps without ambiguity; otherwise the name of the course's TOP code, which faculty should verify.</t>
         </is>
       </c>
     </row>
